--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2110,8 +2110,12 @@
       <c r="A5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>408</v>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED LI-S CF3SO2F SOURCE WASTE-DOSE ALIGNMENT, 2026-10-18. Wickerts et al., Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage, DOI 10.1021/acssuschemeng.3c00141; supporting information Table S2, printed page S7 (PDF page 10), in the updated supporting file https://doi.org/10.1021/acssuschemeng.4c01782.s001. The table specifies 2.1E-1 kg organic waste sent to the market for spent solvent mixture, RoW, per 1 kg CF3SO2F output. Align the workbook treatment purchase from -0.22 to -0.21 kg/kg, retaining the negative waste-consumer sign. The source rounded material inputs 0.66 kg methanesulfonic acid plus 0.55 kg hydrogen fluoride minus 1 kg product also give 0.21 kg residual; this aggregate check is NOT an element-balanced reaction or validation of actual waste composition, water/hydrogen fates or industrial yield. The historical reason for the workbook value 0.22 is not established. Do not attribute this discrepancy to the 2024 published erratum: that correction concerns end-of-life tables S35/S36/S38, results S41 and Figure S17. The source generic 95 percent reaction yield, electricity proxy and spent-solvent treatment are retained modelling assumptions, not validated current industrial measurements. Keep all other material doses, 30 kWh electricity, chemical-factory formula/cache, supplier/product/geography, one-kg reference output, other chemical recipes and downstream battery capacity, density, cycle life and lifetime/per-MJ allocations unchanged. No new treatment route, recovery credit, primary/secondary share or global recipe renormalization is introduced. This is a small source-table alignment, not a demonstrated major critical-metal driver. The larger Li-S recipe/density, LiTFSI yield and silica template issues remain unresolved. Current net system metal effects remain unquantified without a full rebuild.
+PREVIOUS SOURCE NOTES:
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -2291,7 +2295,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="5">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -8700,8 +8700,12 @@
       <c r="A491" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B491" s="16" t="s">
-        <v>413</v>
+      <c r="B491" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S CELL/MODULE METADATA CLARIFICATION, 2026-10-18. The implemented 150 Wh/kg (0.150 kWh/kg) is a CELL-specific reference, not energy per kg module. The existing module recipe contains 408*0.046/24.971 = 0.7515918465419887 kg cell/kg module, giving 0.1127387769812983 kWh/kg module at that cell reference. At the inherited 1500 cycles, 225 kWh/kg applies to CELL mass; the corresponding reference is 169.10816547194747 kWh/kg MODULE. Market output is 1 kg battery module, not a 321 kg system (that was a copied Li-O2 label). These are explanatory conversions under existing assumptions; no recipe, density trajectory, cycle life, replacement or per-MJ allocation is changed. IMPORTANT UNRESOLVED DESIGN GAP: the Wickerts composition reference uses a 500 Wh/kg cell design, whereas the implemented baseline is 150 Wh/kg; this documentation does not reconcile their physical designs or validate complete BMS/cooling coverage. Historical statements below are retained only as history and the cell/module clarification above takes precedence.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Specific energy density: 150 Wh/kg. Projected up to 500 Wh/kg in an optimistic future || Cycle life: 1500 || Lifetime: 225 kWh/kg.Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.2">
@@ -8984,8 +8988,12 @@
       <c r="A510" t="s">
         <v>1</v>
       </c>
-      <c r="B510" s="28" t="s">
-        <v>413</v>
+      <c r="B510" s="28" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S CELL/MODULE METADATA CLARIFICATION, 2026-10-18. The implemented 150 Wh/kg (0.150 kWh/kg) is a CELL-specific reference, not energy per kg module. The existing module recipe contains 408*0.046/24.971 = 0.7515918465419887 kg cell/kg module, giving 0.1127387769812983 kWh/kg module at that cell reference. At the inherited 1500 cycles, 225 kWh/kg applies to CELL mass; the corresponding reference is 169.10816547194747 kWh/kg MODULE. Market output is 1 kg battery module, not a 321 kg system (that was a copied Li-O2 label). These are explanatory conversions under existing assumptions; no recipe, density trajectory, cycle life, replacement or per-MJ allocation is changed. IMPORTANT UNRESOLVED DESIGN GAP: the Wickerts composition reference uses a 500 Wh/kg cell design, whereas the implemented baseline is 150 Wh/kg; this documentation does not reconcile their physical designs or validate complete BMS/cooling coverage. Historical statements below are retained only as history and the cell/module clarification above takes precedence.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Specific energy density: 150 Wh/kg. Projected up to 500 Wh/kg in an optimistic future || Cycle life: 1500 || Lifetime: 225 kWh/kg.Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.2">
@@ -9087,8 +9095,10 @@
         <f>B513</f>
         <v>battery, Li-S</v>
       </c>
-      <c r="H518" t="s">
-        <v>446</v>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Reference output: 1 kg battery module supplied by this market. The implemented cell reference is 150 Wh/kg cell; at 0.7515918465419887 kg cell/kg module this corresponds to 112.7387769812983 Wh/kg module. The former 321 kg system statement was copied from Li-O2 and is not a Li-S source basis. Quantities and density trajectory unchanged; source-design and equipment-coverage gaps remain unresolved.</t>
+        </is>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -9993,8 +9993,12 @@
       <c r="A587" t="s">
         <v>1</v>
       </c>
-      <c r="B587" t="s">
-        <v>410</v>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S BMS FASTENER SOURCE-CONFLICT NOTE, 2026-10-18. The adapted Wickerts supporting information Table S26 lists IBIS fasteners at 2.8E-3 kg per BMS inventory, while its cited original Ellingsen et al. (2014) supporting-information detailed BMS component inventory lists IBIS fasteners at 2.8E-2 kg. The original source therefore supports retaining the existing 0.028 kg fastener input (B602). Do not silently reduce it tenfold to match the adapted table. This records an unresolved source conflict; it does not validate complete BMS sizing, module/rack allocation, cooling coverage or metal composition. All BMS quantities and suppliers remain unchanged.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+This activity is aggregated to match the requirements of one battery rack, as it is modelled in the lithium-sulfur study. This includes both the BMS on a module level as well as on the rack level. BMS=battery management system. PCB=printed circut board. Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -6607,8 +6607,12 @@
       <c r="A347" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B347" s="16" t="s">
-        <v>408</v>
+      <c r="B347" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -6707,7 +6711,7 @@
         <v>116</v>
       </c>
       <c r="B356" s="5">
-        <v>0.68</v>
+        <v>0.28</v>
       </c>
       <c r="C356" t="s">
         <v>7</v>
@@ -6727,7 +6731,7 @@
         <v>40</v>
       </c>
       <c r="B357" s="5">
-        <v>0.10199999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="C357" t="s">
         <v>7</v>
@@ -6747,7 +6751,7 @@
         <v>118</v>
       </c>
       <c r="B358" s="4">
-        <v>6.3E-2</v>
+        <v>0.044</v>
       </c>
       <c r="C358" t="s">
         <v>7</v>
@@ -6767,7 +6771,7 @@
         <v>336</v>
       </c>
       <c r="B359" s="5">
-        <v>0.11600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="C359" t="s">
         <v>7</v>
@@ -6787,7 +6791,7 @@
         <v>333</v>
       </c>
       <c r="B360" s="5">
-        <v>0.10199999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="C360" t="s">
         <v>7</v>
@@ -6879,7 +6883,7 @@
         <v>53</v>
       </c>
       <c r="B364" s="4">
-        <v>-6.3E-2</v>
+        <v>-0.054</v>
       </c>
       <c r="C364" t="s">
         <v>7</v>
@@ -7961,8 +7965,12 @@
       <c r="A440" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B440" s="26" t="s">
-        <v>442</v>
+      <c r="B440" s="26" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+A cell weight of 46 g is modeled, due to the slight difference in cell weight of the different cell compositions. The number of formed cells required to provide the function depends on the specific energy density. Consequently, fewer cells are required in the technical performance and combined scenarios because of the higher specific energy density considered in those scenarios. SI. S3.6.6. Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
@@ -8061,8 +8069,8 @@
         <v>334</v>
       </c>
       <c r="B449" s="3">
-        <f>7.4/1000*(1/0.046)</f>
-        <v>0.16086956521739132</v>
+        <f>0.004/0.047319</f>
+        <v>0.08453264016568397</v>
       </c>
       <c r="C449" t="s">
         <v>7</v>
@@ -8085,8 +8093,8 @@
         <v>335</v>
       </c>
       <c r="B450" s="3">
-        <f>4.6/1000*(1/0.046)</f>
-        <v>0.1</v>
+        <f>0.006/0.047319</f>
+        <v>0.12679896024852597</v>
       </c>
       <c r="C450" t="s">
         <v>7</v>
@@ -8109,8 +8117,8 @@
         <v>337</v>
       </c>
       <c r="B451" s="3">
-        <f>11/1000*(1/0.046)</f>
-        <v>0.23913043478260868</v>
+        <f>0.008/0.047319</f>
+        <v>0.16906528033136795</v>
       </c>
       <c r="C451" t="s">
         <v>7</v>
@@ -8133,8 +8141,8 @@
         <v>338</v>
       </c>
       <c r="B452" s="3">
-        <f>20/1000*(1/0.046)</f>
-        <v>0.43478260869565222</v>
+        <f>0.029/0.047319</f>
+        <v>0.6128616412012089</v>
       </c>
       <c r="C452" t="s">
         <v>7</v>
@@ -8157,8 +8165,8 @@
         <v>339</v>
       </c>
       <c r="B453" s="3">
-        <f>0.13/1000*(1/0.046)</f>
-        <v>2.8260869565217396E-3</v>
+        <f>0.00013/0.047319</f>
+        <v>0.0027473108053847287</v>
       </c>
       <c r="C453" t="s">
         <v>7</v>
@@ -8181,8 +8189,8 @@
         <v>341</v>
       </c>
       <c r="B454" s="3">
-        <f>0.12/1000*(1/0.046)</f>
-        <v>2.6086956521739128E-3</v>
+        <f>0.00012/0.047319</f>
+        <v>0.002535979204970519</v>
       </c>
       <c r="C454" t="s">
         <v>7</v>
@@ -8205,8 +8213,8 @@
         <v>340</v>
       </c>
       <c r="B455" s="3">
-        <f>0.069/1000*(1/0.046)</f>
-        <v>1.5000000000000002E-3</v>
+        <f>6.9e-05/0.047319</f>
+        <v>0.0014581880428580485</v>
       </c>
       <c r="C455" t="s">
         <v>7</v>
@@ -8229,8 +8237,8 @@
         <v>51</v>
       </c>
       <c r="B456" s="3">
-        <f>31/1000*(1/0.046)</f>
-        <v>0.67391304347826086</v>
+        <f>0.031/0.047319</f>
+        <v>0.6551279612840508</v>
       </c>
       <c r="C456" t="s">
         <v>7</v>
@@ -8253,8 +8261,8 @@
         <v>22</v>
       </c>
       <c r="B457" s="13">
-        <f>0.046*(1/0.046)</f>
-        <v>1</v>
+        <f>0.046/0.047319</f>
+        <v>0.9721253619053657</v>
       </c>
       <c r="C457" t="s">
         <v>23</v>
@@ -8274,8 +8282,8 @@
         <v>49</v>
       </c>
       <c r="B458" s="23">
-        <f>-31/1000000*(1/0.046)</f>
-        <v>-6.7391304347826086E-4</v>
+        <f>-3.1e-05/0.047319</f>
+        <v>-0.0006551279612840509</v>
       </c>
       <c r="C458" t="s">
         <v>45</v>
@@ -8308,8 +8316,12 @@
       <c r="A461" t="s">
         <v>1</v>
       </c>
-      <c r="B461" t="s">
-        <v>445</v>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141. Manufacturing of Li-S cells was based on the work by Chordia, M.; Nordelöf, A.; Ellingsen, L. A.-W. Environmental life cycle implications of upscaling lithium-ion battery production. Int. J. Life Cycle Assess. 2021, 26, 2024– 2039,  DOI: 10.1007/s11367-021-01976-0 8. Note that the factory construction and operation is included in this activity, and not in the "1 kWh storage capacity" as it is in the supporting information.</t>
+        </is>
       </c>
       <c r="H461" s="5"/>
     </row>
@@ -8426,8 +8438,8 @@
         <v>22</v>
       </c>
       <c r="B471" s="5">
-        <f>0.225*(1/0.046)</f>
-        <v>4.8913043478260869</v>
+        <f>0.225/0.047319</f>
+        <v>4.754961009319723</v>
       </c>
       <c r="C471" t="s">
         <v>23</v>
@@ -8450,8 +8462,8 @@
         <v>342</v>
       </c>
       <c r="B472" s="13">
-        <f>0.0000000115*(1/0.046)</f>
-        <v>2.5000000000000004E-7</v>
+        <f>1.15e-08/0.047319</f>
+        <v>2.4303134047634144e-07</v>
       </c>
       <c r="C472" t="s">
         <v>6</v>
@@ -8702,7 +8714,9 @@
       </c>
       <c r="B491" s="16" t="inlineStr">
         <is>
-          <t>APPROVED Li-S CELL/MODULE METADATA CLARIFICATION, 2026-10-18. The implemented 150 Wh/kg (0.150 kWh/kg) is a CELL-specific reference, not energy per kg module. The existing module recipe contains 408*0.046/24.971 = 0.7515918465419887 kg cell/kg module, giving 0.1127387769812983 kWh/kg module at that cell reference. At the inherited 1500 cycles, 225 kWh/kg applies to CELL mass; the corresponding reference is 169.10816547194747 kWh/kg MODULE. Market output is 1 kg battery module, not a 321 kg system (that was a copied Li-O2 label). These are explanatory conversions under existing assumptions; no recipe, density trajectory, cycle life, replacement or per-MJ allocation is changed. IMPORTANT UNRESOLVED DESIGN GAP: the Wickerts composition reference uses a 500 Wh/kg cell design, whereas the implemented baseline is 150 Wh/kg; this documentation does not reconcile their physical designs or validate complete BMS/cooling coverage. Historical statements below are retained only as history and the cell/module clarification above takes precedence.
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED Li-S CELL/MODULE METADATA CLARIFICATION, 2026-10-18. The implemented 150 Wh/kg (0.150 kWh/kg) is a CELL-specific reference, not energy per kg module. The existing module recipe contains 408*0.046/24.971 = 0.7515918465419887 kg cell/kg module, giving 0.1127387769812983 kWh/kg module at that cell reference. At the inherited 1500 cycles, 225 kWh/kg applies to CELL mass; the corresponding reference is 169.10816547194747 kWh/kg MODULE. Market output is 1 kg battery module, not a 321 kg system (that was a copied Li-O2 label). These are explanatory conversions under existing assumptions; no recipe, density trajectory, cycle life, replacement or per-MJ allocation is changed. IMPORTANT UNRESOLVED DESIGN GAP: the Wickerts composition reference uses a 500 Wh/kg cell design, whereas the implemented baseline is 150 Wh/kg; this documentation does not reconcile their physical designs or validate complete BMS/cooling coverage. Historical statements below are retained only as history and the cell/module clarification above takes precedence.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Specific energy density: 150 Wh/kg. Projected up to 500 Wh/kg in an optimistic future || Cycle life: 1500 || Lifetime: 225 kWh/kg.Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
         </is>
@@ -8804,8 +8818,8 @@
         <v>440</v>
       </c>
       <c r="B500" s="5">
-        <f>408*0.046/24.971</f>
-        <v>0.75159184654198874</v>
+        <f>19.306152/25.509152</f>
+        <v>0.7568323713779275</v>
       </c>
       <c r="C500" t="s">
         <v>7</v>
@@ -8828,8 +8842,8 @@
         <v>344</v>
       </c>
       <c r="B501" s="5">
-        <f>0.275/24.971</f>
-        <v>1.1012774818789798E-2</v>
+        <f>0.275/25.509152</f>
+        <v>0.010780444602784132</v>
       </c>
       <c r="C501" t="s">
         <v>7</v>
@@ -8849,8 +8863,8 @@
         <v>345</v>
       </c>
       <c r="B502" s="5">
-        <f>0.593/24.971</f>
-        <v>2.3747547154699448E-2</v>
+        <f>0.593/25.509152</f>
+        <v>0.023246558725276322</v>
       </c>
       <c r="C502" t="s">
         <v>7</v>
@@ -8870,8 +8884,8 @@
         <v>346</v>
       </c>
       <c r="B503" s="4">
-        <f>0.085/24.971</f>
-        <v>3.4039485803532099E-3</v>
+        <f>0.085/25.509152</f>
+        <v>0.003332137422678731</v>
       </c>
       <c r="C503" t="s">
         <v>7</v>
@@ -8891,8 +8905,8 @@
         <v>36</v>
       </c>
       <c r="B504" s="7">
-        <f>2.75/24.971</f>
-        <v>0.11012774818789796</v>
+        <f>2.75/25.509152</f>
+        <v>0.1078044460278413</v>
       </c>
       <c r="C504" t="s">
         <v>7</v>
@@ -8915,8 +8929,8 @@
         <v>137</v>
       </c>
       <c r="B505" s="7">
-        <f>2.5/24.971</f>
-        <v>0.10011613471627087</v>
+        <f>2.5/25.509152</f>
+        <v>0.0980040418434921</v>
       </c>
       <c r="C505" t="s">
         <v>7</v>
@@ -8936,8 +8950,8 @@
         <v>18</v>
       </c>
       <c r="B506" s="7">
-        <f>2.75/24.971</f>
-        <v>0.11012774818789796</v>
+        <f>2.75/25.509152</f>
+        <v>0.1078044460278413</v>
       </c>
       <c r="C506" t="s">
         <v>7</v>
@@ -8957,8 +8971,8 @@
         <v>139</v>
       </c>
       <c r="B507" s="13">
-        <f>2.5/24.971</f>
-        <v>0.10011613471627087</v>
+        <f>2.5/25.509152</f>
+        <v>0.0980040418434921</v>
       </c>
       <c r="C507" t="s">
         <v>7</v>
@@ -8990,7 +9004,9 @@
       </c>
       <c r="B510" s="28" t="inlineStr">
         <is>
-          <t>APPROVED Li-S CELL/MODULE METADATA CLARIFICATION, 2026-10-18. The implemented 150 Wh/kg (0.150 kWh/kg) is a CELL-specific reference, not energy per kg module. The existing module recipe contains 408*0.046/24.971 = 0.7515918465419887 kg cell/kg module, giving 0.1127387769812983 kWh/kg module at that cell reference. At the inherited 1500 cycles, 225 kWh/kg applies to CELL mass; the corresponding reference is 169.10816547194747 kWh/kg MODULE. Market output is 1 kg battery module, not a 321 kg system (that was a copied Li-O2 label). These are explanatory conversions under existing assumptions; no recipe, density trajectory, cycle life, replacement or per-MJ allocation is changed. IMPORTANT UNRESOLVED DESIGN GAP: the Wickerts composition reference uses a 500 Wh/kg cell design, whereas the implemented baseline is 150 Wh/kg; this documentation does not reconcile their physical designs or validate complete BMS/cooling coverage. Historical statements below are retained only as history and the cell/module clarification above takes precedence.
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED Li-S CELL/MODULE METADATA CLARIFICATION, 2026-10-18. The implemented 150 Wh/kg (0.150 kWh/kg) is a CELL-specific reference, not energy per kg module. The existing module recipe contains 408*0.046/24.971 = 0.7515918465419887 kg cell/kg module, giving 0.1127387769812983 kWh/kg module at that cell reference. At the inherited 1500 cycles, 225 kWh/kg applies to CELL mass; the corresponding reference is 169.10816547194747 kWh/kg MODULE. Market output is 1 kg battery module, not a 321 kg system (that was a copied Li-O2 label). These are explanatory conversions under existing assumptions; no recipe, density trajectory, cycle life, replacement or per-MJ allocation is changed. IMPORTANT UNRESOLVED DESIGN GAP: the Wickerts composition reference uses a 500 Wh/kg cell design, whereas the implemented baseline is 150 Wh/kg; this documentation does not reconcile their physical designs or validate complete BMS/cooling coverage. Historical statements below are retained only as history and the cell/module clarification above takes precedence.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Specific energy density: 150 Wh/kg. Projected up to 500 Wh/kg in an optimistic future || Cycle life: 1500 || Lifetime: 225 kWh/kg.Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
         </is>
@@ -9097,7 +9113,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Reference output: 1 kg battery module supplied by this market. The implemented cell reference is 150 Wh/kg cell; at 0.7515918465419887 kg cell/kg module this corresponds to 112.7387769812983 Wh/kg module. The former 321 kg system statement was copied from Li-O2 and is not a Li-S source basis. Quantities and density trajectory unchanged; source-design and equipment-coverage gaps remain unresolved.</t>
+          <t>One kg baseline engineering Li-S module; cell47.319g,408cells/module, module25.509152kg,150Wh/kg cell. See current activity comment; older copied whole-system labels are superseded.</t>
         </is>
       </c>
     </row>
@@ -12335,8 +12351,12 @@
       <c r="A750" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B750" s="16" t="s">
-        <v>408</v>
+      <c r="B750" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED Li-S BASE-DESIGN ENGINEERING RECONCILIATION, item15, 2026-10-18. Wickerts corrected SI, DOI10.1021/acssuschemeng.4c01782.s001 Tables S19/S21: use baseline B recipe with the existing150 Wh/kg-cell and1500-cycle reference, rather than technical T ingredients associated with500 Wh/kg. Per cell: Li4g, separator6g, cathode8g, electrolyte29g, pouch.13g, negative tab.12g, positive tab.069g. Detailed retained masses sum47.319g, conflicting with source46g average. Adopt47.319g as the explicit engineering mass basis (not a measured corrected source cell); no arbitrary rescaling of individual ingredients. At150 Wh/kg this is7.09785 Wh/cell. Cathode B perkg: sulfur.28, CMK3.22, PVDF.13, acetonitrile.044, foil.38, organic waste-.054; inputs1.054kg=1kg product+.054kg waste. Preserve process-specific energy and transport. Source PVDF binder uses the existing polyvinylfluoride supply as an explicitly retained cross-version fluoropolymer proxy; exact binder chemistry remains a coverage/model gap, not a verified PVDF route. Per-cell assembly/formation/factory requirements retain their source cell amounts and are divided by47.319g. Module408cells=19.306152kg plus.275Al busbar+.593bimetal+.085Cu+2.75PP+2.5steel =25.509152kg. Cell share is0.7568323713779275. The mobile capacity market normalizes exactly to1 gross kWh at.150kWh/kg-cell, with.120-.180 endpoints and paired waste masses. Future density factors remain the existing relative learning assumption with fixed recipe; this does not validate a future physical cell design, cycle aging or calendar life. Controls/cooling are treated separately under item13. Source average-mass conflict and future recipe evolution remain explicit gaps. This supersedes older24.971kg-module/46g-cell and500Wh/kg-composition statements below.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.2">
@@ -12432,8 +12452,8 @@
         <v>343</v>
       </c>
       <c r="B759">
-        <f>16*24.971</f>
-        <v>399.536</v>
+        <f>16*25.509152</f>
+        <v>408.146432</v>
       </c>
       <c r="C759" t="s">
         <v>7</v>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -4351,8 +4351,12 @@
       <c r="A168" t="s">
         <v>1</v>
       </c>
-      <c r="B168" t="s">
-        <v>412</v>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>APPROVED SALT-SPECIFIC ENGINEERING REFERENCE, item16, 2026-10-18. CN112536014B Example3 https://patents.google.com/patent/CN112536014B/en reports water:HTFSI:Li2CO3=2.8:7.54-7.56:1,110-115C neutralization, spray drying and99.1percent isolated LiTFSI yield. Adopt midpoint7.55, pure HTFSI and battery-grade carbonate as acid-limited feeds; consistent atomic masses Li6.94,H1.008,C12.011,F18.998403,N14.007,O15.999,S32.06g/mol. Perkg isolated salt: HTFSI=0.988230515068844, carbonate=0.13089145894951576, addedwater=0.3664960850586441kg. Assume complete acid conversion before0.9percent isolation loss: CO2=0.0773467098163841kg; excess carbonate=0.0010318008133847756kg and lost LiTFSI=0.00908173562058523kg. Filter residue and salt loss are routed to existing generic wastewater as an explicit hazardous-salt fate proxy, not credited recovery; wastewater inventory does not resolve fluorinated chemistry. Assume0.1kWh/kg auxiliaries, heat=((feedwater+neutralizationwater)*(4.18kJ/kg/K*75K+2.26MJ/kg)+0.5MJ)/0.70=2.1780844732991187MJ/kg; this is an engineering drying estimate, not measured patent utility data. Assume drying water is condensed and collected with salt losses/excess carbonate: the wastewater mass includes feedwater, stoichiometric neutralization water and residues at1000kg/m3. No additional dilution water is invented. Condensate collection and generic wastewater are fate proxies; dedicated fluorinated-salt treatment remains unrepresented. Preserve factory proxy4e-10unit/kg. Upstream HTFSI multistep synthesis remains an inherited source/proxy uncertainty; this corrects the final salt route without transferring unrelated LiPF6 yield. Sensitivities:95-99.1percent isolation yield,50-90percent thermal efficiency; patent scale-up, purification utilities and emissions remain gaps.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+this is LiTFSI. Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -4451,7 +4455,7 @@
         <v>328</v>
       </c>
       <c r="B177" s="7">
-        <v>1.5</v>
+        <v>0.988230515068844</v>
       </c>
       <c r="C177" t="s">
         <v>7</v>
@@ -4471,7 +4475,7 @@
         <v>395</v>
       </c>
       <c r="B178" s="5">
-        <v>0.27</v>
+        <v>0.13089145894951576</v>
       </c>
       <c r="C178" t="s">
         <v>7</v>
@@ -4494,7 +4498,7 @@
         <v>51</v>
       </c>
       <c r="B179" s="18">
-        <v>15</v>
+        <v>0.3664960850586441</v>
       </c>
       <c r="C179" t="s">
         <v>7</v>
@@ -4535,7 +4539,7 @@
         <v>22</v>
       </c>
       <c r="B181" s="7">
-        <v>5.5</v>
+        <v>0.1</v>
       </c>
       <c r="C181" t="s">
         <v>23</v>
@@ -4551,14 +4555,18 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>86</v>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
       </c>
       <c r="B182" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="C182" t="s">
-        <v>7</v>
+        <v>2.1780844732991187</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
       </c>
       <c r="E182" t="s">
         <v>17</v>
@@ -4566,8 +4574,10 @@
       <c r="F182" t="s">
         <v>15</v>
       </c>
-      <c r="G182" t="s">
-        <v>87</v>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -4575,7 +4585,7 @@
         <v>49</v>
       </c>
       <c r="B183" s="4">
-        <v>-1.6E-2</v>
+        <v>-0.00040827134926061976</v>
       </c>
       <c r="C183" t="s">
         <v>45</v>
@@ -4598,7 +4608,7 @@
         <v>287</v>
       </c>
       <c r="B184" s="4">
-        <v>7.6999999999999999E-2</v>
+        <v>0.0773467098163841</v>
       </c>
       <c r="C184" t="s">
         <v>7</v>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -5420,8 +5420,12 @@
       <c r="A250" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B250" s="16" t="s">
-        <v>408</v>
+      <c r="B250" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED ELEMENT-BALANCED TEMPLATE ENGINEERING REFERENCE, item17, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 Tables S15/S16 inherits Jun etal DOI10.1021/ja002261e. Original1.1kg TEOS cannot supply1kg drySiO2: theoretical1.1*60.0843/208.328kg. Treat the reported recipe as a batch and assume95percent isolated silicon yield, giving0.3013905643984486kg SBA15. Scale ALL batch reagents, electricity and factory together by3.3179539047478803perkg drySBA15. This95percent yield is an engineering assumption, not a reported measurement; morphology/wash losses/calcination are not fully resolved. CMK3 original2.1kg sucrose contains less than1kgcarbon; assume95percent carbon retention after pyrolysis, giving0.8400417182179777kg drycarbon per originalbatch. Scale template, sucrose, sulfuricacid,water,electricity,factory together by1.190417068953849. HF must dissolve SiO2: SiO2+6HF-&gt;H2SiF6+2H2O; use5percent molar excess, 2.0977184056400757kgHF/kgtemplate before carbon-batch normalization. No template/solvent recovery credit. Future energy efficiency, actual carbon retention, calcination emissions, alcohol/acid washes and fluorosilicate treatment remain coverage gaps; omitted flows are not zero emissions. Source factory/energy remain batch proxies rather than measured scale-up utilities. Sensitivities: silicon isolation80-100percent; carbon retention50-100percent; HF excess0-20percent. This is joint mass/energy normalization, not an isolated TEOS adjustment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -5517,7 +5521,7 @@
         <v>331</v>
       </c>
       <c r="B259" s="5">
-        <v>0.52</v>
+        <v>1.7253360304688978</v>
       </c>
       <c r="C259" t="s">
         <v>7</v>
@@ -5537,7 +5541,7 @@
         <v>102</v>
       </c>
       <c r="B260" s="7">
-        <v>1.1000000000000001</v>
+        <v>3.6497492952226684</v>
       </c>
       <c r="C260" t="s">
         <v>7</v>
@@ -5557,7 +5561,7 @@
         <v>51</v>
       </c>
       <c r="B261" s="18">
-        <v>18</v>
+        <v>59.72317028546185</v>
       </c>
       <c r="C261" t="s">
         <v>7</v>
@@ -5577,7 +5581,7 @@
         <v>104</v>
       </c>
       <c r="B262" s="7">
-        <v>1.1000000000000001</v>
+        <v>3.6497492952226684</v>
       </c>
       <c r="C262" t="s">
         <v>7</v>
@@ -5597,8 +5601,8 @@
         <v>38</v>
       </c>
       <c r="B263">
-        <f>4*10^-10</f>
-        <v>4.0000000000000001E-10</v>
+        <f>1.3271815618991522e-09</f>
+        <v>1.3271815618991522e-09</v>
       </c>
       <c r="C263" t="s">
         <v>6</v>
@@ -5618,7 +5622,7 @@
         <v>22</v>
       </c>
       <c r="B264" s="18">
-        <v>17</v>
+        <v>56.405216380713966</v>
       </c>
       <c r="C264" t="s">
         <v>23</v>
@@ -5654,8 +5658,12 @@
       <c r="A269" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B269" s="16" t="s">
-        <v>408</v>
+      <c r="B269" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED ELEMENT-BALANCED TEMPLATE ENGINEERING REFERENCE, item17, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 Tables S15/S16 inherits Jun etal DOI10.1021/ja002261e. Original1.1kg TEOS cannot supply1kg drySiO2: theoretical1.1*60.0843/208.328kg. Treat the reported recipe as a batch and assume95percent isolated silicon yield, giving0.3013905643984486kg SBA15. Scale ALL batch reagents, electricity and factory together by3.3179539047478803perkg drySBA15. This95percent yield is an engineering assumption, not a reported measurement; morphology/wash losses/calcination are not fully resolved. CMK3 original2.1kg sucrose contains less than1kgcarbon; assume95percent carbon retention after pyrolysis, giving0.8400417182179777kg drycarbon per originalbatch. Scale template, sucrose, sulfuricacid,water,electricity,factory together by1.190417068953849. HF must dissolve SiO2: SiO2+6HF-&gt;H2SiF6+2H2O; use5percent molar excess, 2.0977184056400757kgHF/kgtemplate before carbon-batch normalization. No template/solvent recovery credit. Future energy efficiency, actual carbon retention, calcination emissions, alcohol/acid washes and fluorosilicate treatment remain coverage gaps; omitted flows are not zero emissions. Source factory/energy remain batch proxies rather than measured scale-up utilities. Sensitivities: silicon isolation80-100percent; carbon retention50-100percent; HF excess0-20percent. This is joint mass/energy normalization, not an isolated TEOS adjustment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
@@ -5751,7 +5759,7 @@
         <v>332</v>
       </c>
       <c r="B278">
-        <v>1</v>
+        <v>1.190417068953849</v>
       </c>
       <c r="C278" t="s">
         <v>7</v>
@@ -5771,7 +5779,7 @@
         <v>107</v>
       </c>
       <c r="B279" s="7">
-        <v>2.1</v>
+        <v>2.499875844803083</v>
       </c>
       <c r="C279" t="s">
         <v>7</v>
@@ -5791,7 +5799,7 @@
         <v>56</v>
       </c>
       <c r="B280" s="5">
-        <v>0.23</v>
+        <v>0.2737959258593853</v>
       </c>
       <c r="C280" t="s">
         <v>7</v>
@@ -5811,7 +5819,7 @@
         <v>77</v>
       </c>
       <c r="B281" s="7">
-        <v>1</v>
+        <v>2.4971597959326</v>
       </c>
       <c r="C281" t="s">
         <v>7</v>
@@ -5831,7 +5839,7 @@
         <v>51</v>
       </c>
       <c r="B282" s="18">
-        <v>10</v>
+        <v>11.90417068953849</v>
       </c>
       <c r="C282" t="s">
         <v>7</v>
@@ -5851,8 +5859,8 @@
         <v>38</v>
       </c>
       <c r="B283">
-        <f>4*10^-10</f>
-        <v>4.0000000000000001E-10</v>
+        <f>4.761668275815395e-10</f>
+        <v>4.761668275815395e-10</v>
       </c>
       <c r="C283" t="s">
         <v>6</v>
@@ -5872,7 +5880,7 @@
         <v>22</v>
       </c>
       <c r="B284" s="18">
-        <v>24</v>
+        <v>28.570009654892374</v>
       </c>
       <c r="C284" t="s">
         <v>23</v>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1076"/>
+  <dimension ref="A1:Q1131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -15483,6 +15483,1059 @@
     <row r="1076" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A1076" s="1"/>
     </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1081">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1088">
+        <v>1</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1089">
+        <v>0.49</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>high voltage system production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B1090">
+        <v>2.8</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>high voltage system</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>low voltage system production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B1091">
+        <v>1.2</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>low voltage system</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>IBIS fasteners production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B1092">
+        <v>0.028</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>IBIS fasteners</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>battery liquid cooling, 10 kg engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1097">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>battery liquid cooling, 10 kg engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>battery liquid cooling, 10 kg engineering reference</t>
+        </is>
+      </c>
+      <c r="B1104">
+        <v>1</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>battery liquid cooling, 10 kg engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1105">
+        <v>9.08</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1106">
+        <v>0.23</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>market for polyvinylchloride, bulk polymerised</t>
+        </is>
+      </c>
+      <c r="B1107">
+        <v>0.0072</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>polyvinylchloride, bulk polymerised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>synthetic rubber production</t>
+        </is>
+      </c>
+      <c r="B1108">
+        <v>0.0024</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>synthetic rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>silicon production, electronics grade</t>
+        </is>
+      </c>
+      <c r="B1109">
+        <v>0.06</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>silicon, electronics grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1110">
+        <v>0.02</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>market for acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+      <c r="B1111">
+        <v>0.12</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>acrylonitrile-butadiene-styrene copolymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1112">
+        <v>0.48</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1113">
+        <v>9.08</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1114">
+        <v>0.23</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1115">
+        <v>0.1296</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+      <c r="B1127">
+        <v>1</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>battery controls and cooling, 16-module engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1128">
+        <v>1</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1129">
+        <v>1.1</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>battery liquid cooling, 10 kg engineering reference</t>
+        </is>
+      </c>
+      <c r="B1130">
+        <v>1</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>battery liquid cooling, 10 kg engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1131">
+        <v>-15.6176</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1081" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1131"/>
+  <dimension ref="A1:Q1144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -5913,8 +5913,12 @@
       <c r="A289" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B289" s="16" t="s">
-        <v>408</v>
+      <c r="B289" s="16" t="inlineStr">
+        <is>
+          <t>APPROVED LITHIUM-FOIL ROLLING ENGINEERING REFERENCE, item31, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 TableS17 requires lithium-adapted rolling; processing assumptions below are an engineering completion, not reported measurements. Replace the ordinary aluminium-specific rolling service at4.95kgprocessed/kgfinishedLi foil by a dedicated material-neutral mechanical rolling service. Assume0.5kWh electricity perkg rolling throughput, hence2.475kWh perkgfinishedfoil additionally to source2.1kWh generalprocess electricity,4.2MJ cooling and5MJheat retained once. This represents4.95kg cumulative rolling throughput, NOT4.95kg retained lithium or a measured pass count. Assume98percent final lithium retention:1/0.98=1.0204081632653061kg Li from source electrolysis perkgfoil;0.02040816326530612kg process loss. No aluminium feed or aluminium scrap is inherited; ordinary Al rolling elsewhere unchanged. Treat loss through existing hazardous-waste incineration as an explicit reactive-lithium fate proxy; real inert handling/passivation and associated emissions are not modeled. No lithium recovery/secondary-supply credit. Source/reference utilities are engineering proxies; atmosphere/inert gas, lubrication, facility and practical rolling yield/energy remain gaps. Sensitivities90-100percent yield and0.1-1kWh/kg throughput; energy does not scale with yield here because throughput is declared perkgfinishedfoil. No source-specific measured yield is claimed.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
+        </is>
       </c>
     </row>
     <row r="290" spans="1:17" x14ac:dyDescent="0.2">
@@ -6029,8 +6033,10 @@
       </c>
     </row>
     <row r="299" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A299" t="s">
-        <v>21</v>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>lithium foil rolling service, engineering reference</t>
+        </is>
       </c>
       <c r="B299" s="5">
         <v>4.95</v>
@@ -6038,17 +6044,23 @@
       <c r="C299" t="s">
         <v>7</v>
       </c>
-      <c r="E299" t="s">
-        <v>17</v>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="F299" t="s">
         <v>15</v>
       </c>
-      <c r="G299" t="s">
-        <v>21</v>
-      </c>
-      <c r="H299" s="10" t="s">
-        <v>376</v>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>lithium foil rolling service, engineering reference</t>
+        </is>
+      </c>
+      <c r="H299" s="10" t="inlineStr">
+        <is>
+          <t>APPROVED LITHIUM-FOIL ROLLING ENGINEERING REFERENCE, item31, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 TableS17 requires lithium-adapted rolling; processing assumptions below are an engineering completion, not reported measurements. Replace the ordinary aluminium-specific rolling service at4.95kgprocessed/kgfinishedLi foil by a dedicated material-neutral mechanical rolling service. Assume0.5kWh electricity perkg rolling throughput, hence2.475kWh perkgfinishedfoil additionally to source2.1kWh generalprocess electricity,4.2MJ cooling and5MJheat retained once. This represents4.95kg cumulative rolling throughput, NOT4.95kg retained lithium or a measured pass count. Assume98percent final lithium retention:1/0.98=1.0204081632653061kg Li from source electrolysis perkgfoil;0.02040816326530612kg process loss. No aluminium feed or aluminium scrap is inherited; ordinary Al rolling elsewhere unchanged. Treat loss through existing hazardous-waste incineration as an explicit reactive-lithium fate proxy; real inert handling/passivation and associated emissions are not modeled. No lithium recovery/secondary-supply credit. Source/reference utilities are engineering proxies; atmosphere/inert gas, lubrication, facility and practical rolling yield/energy remain gaps. Sensitivities90-100percent yield and0.1-1kWh/kg throughput; energy does not scale with yield here because throughput is declared perkgfinishedfoil. No source-specific measured yield is claimed.</t>
+        </is>
       </c>
       <c r="K299" s="10"/>
       <c r="L299" s="10"/>
@@ -6103,7 +6115,7 @@
         <v>110</v>
       </c>
       <c r="B302" s="5">
-        <v>1</v>
+        <v>1.0204081632653061</v>
       </c>
       <c r="C302" t="s">
         <v>7</v>
@@ -6116,6 +6128,41 @@
       </c>
       <c r="G302" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B303">
+        <v>-0.020408163265306145</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Assumed2percent lithium loss; reactive-metal fate proxy, not validated safe disposal or recovery.</t>
+        </is>
       </c>
     </row>
     <row r="304" spans="1:17" x14ac:dyDescent="0.2">
@@ -16536,6 +16583,197 @@
         </is>
       </c>
     </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>lithium foil rolling service, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>lithium foil rolling service, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 TableS17 requires lithium-adapted rolling; processing assumptions below are an engineering completion, not reported measurements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>APPROVED LITHIUM-FOIL ROLLING ENGINEERING REFERENCE, item31, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 TableS17 requires lithium-adapted rolling; processing assumptions below are an engineering completion, not reported measurements. Replace the ordinary aluminium-specific rolling service at4.95kgprocessed/kgfinishedLi foil by a dedicated material-neutral mechanical rolling service. Assume0.5kWh electricity perkg rolling throughput, hence2.475kWh perkgfinishedfoil additionally to source2.1kWh generalprocess electricity,4.2MJ cooling and5MJheat retained once. This represents4.95kg cumulative rolling throughput, NOT4.95kg retained lithium or a measured pass count. Assume98percent final lithium retention:1/0.98=1.0204081632653061kg Li from source electrolysis perkgfoil;0.02040816326530612kg process loss. No aluminium feed or aluminium scrap is inherited; ordinary Al rolling elsewhere unchanged. Treat loss through existing hazardous-waste incineration as an explicit reactive-lithium fate proxy; real inert handling/passivation and associated emissions are not modeled. No lithium recovery/secondary-supply credit. Source/reference utilities are engineering proxies; atmosphere/inert gas, lubrication, facility and practical rolling yield/energy remain gaps. Sensitivities90-100percent yield and0.1-1kWh/kg throughput; energy does not scale with yield here because throughput is declared perkgfinishedfoil. No source-specific measured yield is claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>lithium foil rolling service, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1143">
+        <v>1</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>lithium foil rolling service, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1144">
+        <v>0.5</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1081" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1144"/>
+  <dimension ref="A1:Q1227"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -15608,7 +15608,9 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
         </is>
       </c>
     </row>
@@ -15694,7 +15696,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery central control board, engineering material reference</t>
         </is>
       </c>
       <c r="B1089">
@@ -15717,7 +15719,7 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery central control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16382,9 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
         </is>
       </c>
     </row>
@@ -16496,7 +16500,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B1129">
@@ -16519,7 +16523,7 @@
       </c>
       <c r="G1129" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -16769,6 +16773,2079 @@
         </is>
       </c>
       <c r="G1144" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+      <c r="B1156">
+        <v>1</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1157">
+        <v>0.00017748693999999999</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1158">
+        <v>4.0023129999999995e-06</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1159">
+        <v>4.174818e-06</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>market for sulfur</t>
+        </is>
+      </c>
+      <c r="B1160">
+        <v>1e-12</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>sulfur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>market for manganese</t>
+        </is>
+      </c>
+      <c r="B1161">
+        <v>2e-12</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1162">
+        <v>4.372259e-06</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1163">
+        <v>1.2388582e-05</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B1164">
+        <v>1.81e-10</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1165">
+        <v>2.33619e-07</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1166">
+        <v>3.4234e-08</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1167">
+        <v>1.79949e-07</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>market for phenolic resin</t>
+        </is>
+      </c>
+      <c r="B1168">
+        <v>4.646803e-06</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>phenolic resin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1169">
+        <v>0.00013785516</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1170">
+        <v>7.74467e-07</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>market for wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="B1171">
+        <v>2.9021567954220318e-05</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>battery central control board, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>battery central control board, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>battery central control board, engineering material reference</t>
+        </is>
+      </c>
+      <c r="B1183">
+        <v>1</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>battery central control board, engineering material reference</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>battery central control board, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1184">
+        <v>0.38152524167561763</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1185">
+        <v>0.2547583243823846</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1186">
+        <v>0.13473684210526318</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1187">
+        <v>9.081632653061226e-05</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1188">
+        <v>1.969387755102041e-06</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B1189">
+        <v>-0.03179377013963477</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B1190">
+        <v>-0.0067368421052631505</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>market for electric connector, peripheral type buss</t>
+        </is>
+      </c>
+      <c r="B1191">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>electric connector, peripheral type buss</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>electric connector, peripheral type buss</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>market for integrated circuit, logic type</t>
+        </is>
+      </c>
+      <c r="B1192">
+        <v>0.010204081632653062</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>integrated circuit, logic type</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>integrated circuit, logic type</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>market for capacitor, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="B1193">
+        <v>0.004081632653061225</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>capacitor, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>capacitor, for surface-mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B1194">
+        <v>0.006122448979591837</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>market for solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="B1195">
+        <v>0.010204081632653062</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1196">
+        <v>0.03272354081632645</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1197">
+        <v>4.081632653061225</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>battery module control board, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>battery module control board, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>battery module control board, engineering material reference</t>
+        </is>
+      </c>
+      <c r="B1209">
+        <v>1</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>battery module control board, engineering material reference</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>battery module control board, engineering material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1210">
+        <v>0.26706766917293234</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1211">
+        <v>0.1783308270676692</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1212">
+        <v>0.1414736842105263</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1213">
+        <v>6.357142857142857e-05</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1214">
+        <v>1.3785714285714285e-06</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>market for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B1215">
+        <v>-0.022255639097744338</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed, Recycled Content cut-off</t>
+        </is>
+      </c>
+      <c r="B1216">
+        <v>-0.0070736842105263075</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>copper scrap, sorted, pressed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+      <c r="B1217">
+        <v>14.285714285714285</v>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>market for electric connector, peripheral type buss</t>
+        </is>
+      </c>
+      <c r="B1218">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>electric connector, peripheral type buss</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>electric connector, peripheral type buss</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>market for integrated circuit, logic type</t>
+        </is>
+      </c>
+      <c r="B1219">
+        <v>0.021428571428571425</v>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>integrated circuit, logic type</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>integrated circuit, logic type</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>market for inductor, miniature radio frequency chip</t>
+        </is>
+      </c>
+      <c r="B1220">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>inductor, miniature radio frequency chip</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>inductor, miniature radio frequency chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>market for diode, glass-, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="B1221">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>diode, glass-, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>diode, glass-, for surface-mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>market for integrated circuit, logic type</t>
+        </is>
+      </c>
+      <c r="B1222">
+        <v>0.005714285714285714</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>integrated circuit, logic type</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>integrated circuit, logic type</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>market for capacitor, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="B1223">
+        <v>0.01297142857142857</v>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>capacitor, for surface-mounting</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>capacitor, for surface-mounting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>market for resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="B1224">
+        <v>0.020371428571428565</v>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>resistor, surface-mounted</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>market for solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="B1225">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1226">
+        <v>0.048099559985714205</v>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1227">
+        <v>15.714285714285714</v>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1227"/>
+  <dimension ref="A1:Q1394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -17467,7 +17467,9 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17880,7 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>market for capacitor, for surface-mounting</t>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
         </is>
       </c>
       <c r="B1193">
@@ -17901,7 +17903,7 @@
       </c>
       <c r="G1193" t="inlineStr">
         <is>
-          <t>capacitor, for surface-mounting</t>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
         </is>
       </c>
       <c r="I1193" t="inlineStr">
@@ -18128,7 +18130,9 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
         </is>
       </c>
     </row>
@@ -18679,11 +18683,11 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>market for capacitor, for surface-mounting</t>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
         </is>
       </c>
       <c r="B1223">
-        <v>0.01297142857142857</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
@@ -18692,7 +18696,7 @@
       </c>
       <c r="D1223" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1223" t="inlineStr">
@@ -18702,7 +18706,7 @@
       </c>
       <c r="G1223" t="inlineStr">
         <is>
-          <t>capacitor, for surface-mounting</t>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
         </is>
       </c>
       <c r="I1223" t="inlineStr">
@@ -18788,7 +18792,7 @@
         </is>
       </c>
       <c r="B1226">
-        <v>0.048099559985714205</v>
+        <v>0.042876559985714206</v>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
@@ -18848,6 +18852,3600 @@
       <c r="I1227" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1239">
+        <v>1</v>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>market for barium carbonate</t>
+        </is>
+      </c>
+      <c r="B1240">
+        <v>0.8462376335278806</v>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>barium carbonate</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>barium carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>market for titanium dioxide</t>
+        </is>
+      </c>
+      <c r="B1241">
+        <v>0.3424874887967374</v>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>titanium dioxide</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>titanium dioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1242">
+        <v>3</v>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1243">
+        <v>0.5</v>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1244">
+        <v>0.18872512232461802</v>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1256">
+        <v>1</v>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>market for calcium carbonate, precipitated</t>
+        </is>
+      </c>
+      <c r="B1257">
+        <v>0.5582072404196342</v>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>calcium carbonate, precipitated</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>calcium carbonate, precipitated</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>market for zirconium oxide</t>
+        </is>
+      </c>
+      <c r="B1258">
+        <v>0.6872430967266967</v>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1259">
+        <v>3</v>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1260">
+        <v>0.5</v>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B1261">
+        <v>0.245450337146331</v>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1273">
+        <v>1</v>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1274">
+        <v>0.8673091178650854</v>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1275">
+        <v>0.07412898443291327</v>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1276">
+        <v>0.04447739065974796</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1277">
+        <v>0.05189028910303929</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1278">
+        <v>-0.051890289103039236</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1279">
+        <v>1</v>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1280">
+        <v>5</v>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1292">
+        <v>1</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1293">
+        <v>0.7982456140350878</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1294">
+        <v>0.14210526315789473</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1295">
+        <v>0.05614035087719299</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1296">
+        <v>0.0456140350877193</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1297">
+        <v>-0.052105263157894675</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1298">
+        <v>1</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1299">
+        <v>5</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1311">
+        <v>1</v>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1312">
+        <v>0.8008429926238145</v>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1313">
+        <v>0.0898452664854972</v>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1314">
+        <v>0.11812988741611669</v>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1315">
+        <v>0.02384781764738506</v>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1316">
+        <v>-0.051633298208640606</v>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1317">
+        <v>1</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1318">
+        <v>5</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1330">
+        <v>1</v>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1331">
+        <v>0.8785586942318979</v>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1332">
+        <v>0.10342498366682538</v>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1333">
+        <v>0.04274308746830256</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1334">
+        <v>0.013952406790171306</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1335">
+        <v>-0.05193395860785979</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1336">
+        <v>1</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1337">
+        <v>5</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1349">
+        <v>1</v>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1350">
+        <v>0.8811697139527788</v>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>barium titanate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1351">
+        <v>0.0632577754348972</v>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1352">
+        <v>0.03717781538717643</v>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1353">
+        <v>0.024970174513775215</v>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1354">
+        <v>0.027744638348639127</v>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1355">
+        <v>-0.05171600588186328</v>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1356">
+        <v>1</v>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1357">
+        <v>5</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1369">
+        <v>1</v>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="B1370">
+        <v>0.780701754385965</v>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1371">
+        <v>0.07894736842105263</v>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1372">
+        <v>0.008771929824561403</v>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1373">
+        <v>0.04385964912280702</v>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1374">
+        <v>-0.045614035087719246</v>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1375">
+        <v>1</v>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1376">
+        <v>5</v>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1388">
+        <v>1</v>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1389">
+        <v>7.809999999999999e-05</v>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1390">
+        <v>0.00016199999999999998</v>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1391">
+        <v>0.0007212399999999999</v>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1392">
+        <v>0.00028518</v>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1393">
+        <v>1.897e-05</v>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1394">
+        <v>8.12e-06</v>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>capacitor, C0G, 0402, declared material engineering reference</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1394"/>
+  <dimension ref="A1:Q1488"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -17467,7 +17467,9 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
         </is>
@@ -17915,7 +17917,7 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>market for resistor, surface-mounted</t>
+          <t>thick-film resistor, declared-material engineering reference</t>
         </is>
       </c>
       <c r="B1194">
@@ -17938,7 +17940,7 @@
       </c>
       <c r="G1194" t="inlineStr">
         <is>
-          <t>resistor, surface-mounted</t>
+          <t>thick-film resistor, declared-material engineering reference</t>
         </is>
       </c>
       <c r="I1194" t="inlineStr">
@@ -18130,7 +18132,9 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
         </is>
@@ -18718,11 +18722,11 @@
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>market for resistor, surface-mounted</t>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
         </is>
       </c>
       <c r="B1224">
-        <v>0.020371428571428565</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
@@ -18731,7 +18735,7 @@
       </c>
       <c r="D1224" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1224" t="inlineStr">
@@ -18741,7 +18745,7 @@
       </c>
       <c r="G1224" t="inlineStr">
         <is>
-          <t>resistor, surface-mounted</t>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
         </is>
       </c>
       <c r="I1224" t="inlineStr">
@@ -18792,7 +18796,7 @@
         </is>
       </c>
       <c r="B1226">
-        <v>0.042876559985714206</v>
+        <v>0.055591559985714196</v>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
@@ -22446,6 +22450,2051 @@
       <c r="I1394" t="inlineStr">
         <is>
           <t>capacitor, C0G, 0402, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+      <c r="B1406">
+        <v>1</v>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>platinum group metal, extraction and refinery operations</t>
+        </is>
+      </c>
+      <c r="B1407">
+        <v>0.759536477590405</v>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>ruthenium</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>ruthenium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B1408">
+        <v>0.240463522409595</v>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1409">
+        <v>3</v>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1410">
+        <v>0.5</v>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Engineering PbO oxidation reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps. PbO made from Pb and oxygen at stoichiometry; heat proxy, not measured lead-glass processing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+      <c r="B1422">
+        <v>1</v>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B1423">
+        <v>0.9283195713242441</v>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B1424">
+        <v>0.07168042867575572</v>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1425">
+        <v>3</v>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1437">
+        <v>1</v>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B1438">
+        <v>0.86834512207402</v>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>IAI Area, EU27 &amp; EFTA</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1439">
+        <v>0.0381242158605055</v>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1440">
+        <v>0.028665826622505382</v>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>market for flat glass, uncoated</t>
+        </is>
+      </c>
+      <c r="B1441">
+        <v>0.0012165218361587303</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>flat glass, uncoated</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>flat glass, uncoated</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1442">
+        <v>0.018234219915578283</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1443">
+        <v>0.048878595475191945</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>market for chromium</t>
+        </is>
+      </c>
+      <c r="B1444">
+        <v>0.00027215253605340724</v>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1445">
+        <v>0.04251022613154221</v>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+      <c r="B1446">
+        <v>0.0008327867603234263</v>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>lead oxide, resistor glass engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+      <c r="B1447">
+        <v>0.003469944834680942</v>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>ruthenium dioxide, resistor film engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1448">
+        <v>0.002081966900808565</v>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1449">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1450">
+        <v>1</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1451">
+        <v>5</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1463">
+        <v>1</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B1464">
+        <v>0.86834512207402</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>IAI Area, EU27 &amp; EFTA</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1465">
+        <v>0.03618104675308417</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1466">
+        <v>0.03699369422573964</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>market for flat glass, uncoated</t>
+        </is>
+      </c>
+      <c r="B1467">
+        <v>0.0012165218361587303</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>flat glass, uncoated</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>flat glass, uncoated</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1468">
+        <v>0.018234219915578283</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1469">
+        <v>0.048878595475191945</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>market for chromium</t>
+        </is>
+      </c>
+      <c r="B1470">
+        <v>0.00027215253605340724</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1471">
+        <v>0.04251022613154221</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1472">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1473">
+        <v>1</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1474">
+        <v>5</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1486">
+        <v>1</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1487">
+        <v>0.0004893</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1488">
+        <v>4.6649999999999996e-05</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>zero-ohm jumper, declared-material engineering reference</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1488"/>
+  <dimension ref="A1:Q1566"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -17467,7 +17467,9 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
+          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17847,11 +17849,11 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>market for integrated circuit, logic type</t>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
         </is>
       </c>
       <c r="B1192">
-        <v>0.010204081632653062</v>
+        <v>2.0408163265306123</v>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
@@ -17860,7 +17862,7 @@
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
@@ -17870,7 +17872,7 @@
       </c>
       <c r="G1192" t="inlineStr">
         <is>
-          <t>integrated circuit, logic type</t>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
         </is>
       </c>
       <c r="I1192" t="inlineStr">
@@ -17991,7 +17993,7 @@
         </is>
       </c>
       <c r="B1196">
-        <v>0.03272354081632645</v>
+        <v>0.04263626663673462</v>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
@@ -18132,7 +18134,9 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
+          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18547,11 +18551,11 @@
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>market for integrated circuit, logic type</t>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
         </is>
       </c>
       <c r="B1219">
-        <v>0.021428571428571425</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
@@ -18560,7 +18564,7 @@
       </c>
       <c r="D1219" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1219" t="inlineStr">
@@ -18570,7 +18574,7 @@
       </c>
       <c r="G1219" t="inlineStr">
         <is>
-          <t>integrated circuit, logic type</t>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
         </is>
       </c>
       <c r="I1219" t="inlineStr">
@@ -18652,11 +18656,11 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>market for integrated circuit, logic type</t>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
         </is>
       </c>
       <c r="B1222">
-        <v>0.005714285714285714</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
@@ -18665,7 +18669,7 @@
       </c>
       <c r="D1222" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1222" t="inlineStr">
@@ -18675,7 +18679,7 @@
       </c>
       <c r="G1222" t="inlineStr">
         <is>
-          <t>integrated circuit, logic type</t>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
         </is>
       </c>
       <c r="I1222" t="inlineStr">
@@ -18796,7 +18800,7 @@
         </is>
       </c>
       <c r="B1226">
-        <v>0.055591559985714196</v>
+        <v>0.08030247079999991</v>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
@@ -24495,6 +24499,1989 @@
       <c r="I1488" t="inlineStr">
         <is>
           <t>zero-ohm jumper, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1500">
+        <v>1</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1501">
+        <v>5.935076499999999e-05</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1502">
+        <v>1.36973e-06</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1503">
+        <v>1.1396e-08</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1504">
+        <v>6.671100000000001e-08</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1505">
+        <v>1.7926779999999998e-06</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1505" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1506">
+        <v>8.789149999999999e-06</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1507">
+        <v>1.3915e-06</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1508">
+        <v>9.074999999999999e-09</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1509">
+        <v>6.049999999999999e-08</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1510">
+        <v>6.2740964e-05</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1511">
+        <v>2.1389e-07</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>market for chlorine, gaseous</t>
+        </is>
+      </c>
+      <c r="B1512">
+        <v>7.129999999999999e-10</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>chlorine, gaseous</t>
+        </is>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>chlorine, gaseous</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>market for wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="B1513">
+        <v>9.967440629470673e-06</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1514">
+        <v>0.00014276434799999994</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1526">
+        <v>1</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1527">
+        <v>4.1931086e-05</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1528">
+        <v>8.53e-09</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1529">
+        <v>4.4704e-08</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1530">
+        <v>6.62439e-07</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1531">
+        <v>5.0896739999999994e-06</v>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1532">
+        <v>9.5667e-07</v>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1533">
+        <v>1.2441e-08</v>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>market for lead</t>
+        </is>
+      </c>
+      <c r="B1534">
+        <v>8.58e-10</v>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1535">
+        <v>5.4912e-08</v>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1536">
+        <v>9.9876e-07</v>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>market for phenolic resin</t>
+        </is>
+      </c>
+      <c r="B1537">
+        <v>1.6413549999999999e-06</v>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>phenolic resin</t>
+        </is>
+      </c>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>phenolic resin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1538">
+        <v>4.0095957e-05</v>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1538" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1539">
+        <v>2.34479e-07</v>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1539" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>market for wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="B1540">
+        <v>5.5324678111587985e-06</v>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="I1540" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1541">
+        <v>9.559906199999999e-05</v>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1541" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1552" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1553">
+        <v>1</v>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1553" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1554">
+        <v>2.8695129999999998e-05</v>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1554" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>market for palladium</t>
+        </is>
+      </c>
+      <c r="B1555">
+        <v>6.033e-09</v>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+      <c r="I1555" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>market for silver</t>
+        </is>
+      </c>
+      <c r="B1556">
+        <v>7.7583e-08</v>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="I1556" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1557">
+        <v>6.4927309999999995e-06</v>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1557" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1558">
+        <v>7.17654e-07</v>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1558" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1559">
+        <v>2.4254999999999998e-08</v>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1559" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1560">
+        <v>3.8219999999999994e-08</v>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1560" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1561">
+        <v>9.7022e-08</v>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1561" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1562">
+        <v>7.96e-10</v>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1562" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>market for silica sand</t>
+        </is>
+      </c>
+      <c r="B1563">
+        <v>3.7947141999999996e-05</v>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+      <c r="I1563" t="inlineStr">
+        <is>
+          <t>silica sand</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1564">
+        <v>2.2321799999999998e-07</v>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1564" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>market for wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="B1565">
+        <v>4.5406151645207437e-07</v>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+      <c r="I1565" t="inlineStr">
+        <is>
+          <t>wafer, fabricated, for integrated circuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1566">
+        <v>7.4637181e-05</v>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1566" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1566"/>
+  <dimension ref="A1:Q1590"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -17467,7 +17467,9 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17989,7 +17991,7 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B1196">
@@ -18012,7 +18014,7 @@
       </c>
       <c r="G1196" t="inlineStr">
         <is>
-          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I1196" t="inlineStr">
@@ -18134,7 +18136,9 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18796,7 +18800,7 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>market for printed wiring board, surface mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B1226">
@@ -18819,7 +18823,7 @@
       </c>
       <c r="G1226" t="inlineStr">
         <is>
-          <t>printed wiring board, surface mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I1226" t="inlineStr">
@@ -26480,6 +26484,597 @@
         </is>
       </c>
       <c r="I1566" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1577" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1578">
+        <v>1</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+      <c r="I1578" t="inlineStr">
+        <is>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1579">
+        <v>0.24</v>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1579" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>market for epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="B1580">
+        <v>0.16</v>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+      <c r="I1580" t="inlineStr">
+        <is>
+          <t>epoxy resin, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1581">
+        <v>0.18</v>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1581" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>market for ferrite</t>
+        </is>
+      </c>
+      <c r="B1582">
+        <v>0.15</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="I1582" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1583">
+        <v>0.1</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1583" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B1584">
+        <v>0.09</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1584" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>market for solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="B1585">
+        <v>0.03</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+      <c r="I1585" t="inlineStr">
+        <is>
+          <t>solder, bar, Sn95.5Ag3.9Cu0.6, for electronics industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1586">
+        <v>0.025</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1586" t="inlineStr">
+        <is>
+          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1587">
+        <v>0.005</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1587" t="inlineStr">
+        <is>
+          <t>thick-film resistor, declared-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1588">
+        <v>133.98148035628515</v>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1588" t="inlineStr">
+        <is>
+          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="B1589">
+        <v>104.60353680039248</v>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+      <c r="I1589" t="inlineStr">
+        <is>
+          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1590">
+        <v>2</v>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1590" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1590"/>
+  <dimension ref="A1:Q1632"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -27080,6 +27080,978 @@
         </is>
       </c>
     </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1595">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1601" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1602">
+        <v>1</v>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1602" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>battery cell production, Li-S</t>
+        </is>
+      </c>
+      <c r="B1603">
+        <v>1</v>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>battery cell, LiS</t>
+        </is>
+      </c>
+      <c r="I1603" t="inlineStr">
+        <is>
+          <t>battery cell, LiS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1604">
+        <v>0.309107277</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I1604" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="B1605">
+        <v>0.02462741</v>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="I1605" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B1606">
+        <v>0.208779765</v>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I1606" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B1607">
+        <v>0.599015849</v>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I1607" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1608">
+        <v>-1</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1608" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1613">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1619" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1620">
+        <v>1</v>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1620" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>aluminium busbar production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B1621">
+        <v>0.09496109495736559</v>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>aluminium busbar</t>
+        </is>
+      </c>
+      <c r="I1621" t="inlineStr">
+        <is>
+          <t>aluminium busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>bimetallic busbar production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B1622">
+        <v>0.20477065203533737</v>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>bimetallic busbar</t>
+        </is>
+      </c>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>bimetallic busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>copper busbar production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B1623">
+        <v>0.029351611168640268</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>copper busbar</t>
+        </is>
+      </c>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>copper busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1624">
+        <v>0.9496109495736557</v>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1625">
+        <v>0.8632826814305962</v>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1625" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>market for injection moulding</t>
+        </is>
+      </c>
+      <c r="B1626">
+        <v>0.9496109495736557</v>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1626" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1627">
+        <v>0.8632826814305962</v>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1627" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1628">
+        <v>0.6621006745176354</v>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I1628" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="B1629">
+        <v>0.05275134552274666</v>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="I1629" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B1630">
+        <v>0.44720145243340037</v>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I1630" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B1631">
+        <v>1.2830781647034926</v>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I1631" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1632">
+        <v>-2.1419769891655944</v>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1632" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1081" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -2072,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1632"/>
+  <dimension ref="A1:Q1654"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" bestFit="1" customWidth="1"/>
@@ -17467,7 +17467,9 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t>APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17816,7 +17818,7 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>market for electric connector, peripheral type buss</t>
+          <t>connector, battery control header family, plated-material engineering reference</t>
         </is>
       </c>
       <c r="B1191">
@@ -17839,12 +17841,12 @@
       </c>
       <c r="G1191" t="inlineStr">
         <is>
-          <t>electric connector, peripheral type buss</t>
+          <t>connector, battery control header family, plated-material engineering reference</t>
         </is>
       </c>
       <c r="I1191" t="inlineStr">
         <is>
-          <t>electric connector, peripheral type buss</t>
+          <t>connector, battery control header family, plated-material engineering reference</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18138,9 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t>APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18520,7 +18524,7 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>market for electric connector, peripheral type buss</t>
+          <t>connector, battery control header family, plated-material engineering reference</t>
         </is>
       </c>
       <c r="B1218">
@@ -18543,12 +18547,12 @@
       </c>
       <c r="G1218" t="inlineStr">
         <is>
-          <t>electric connector, peripheral type buss</t>
+          <t>connector, battery control header family, plated-material engineering reference</t>
         </is>
       </c>
       <c r="I1218" t="inlineStr">
         <is>
-          <t>electric connector, peripheral type buss</t>
+          <t>connector, battery control header family, plated-material engineering reference</t>
         </is>
       </c>
     </row>
@@ -28049,6 +28053,527 @@
       <c r="I1632" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>connector, battery control header family, plated-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1637">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>connector, battery control header family, plated-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1643" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1643" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>connector, battery control header family, plated-material engineering reference</t>
+        </is>
+      </c>
+      <c r="B1644">
+        <v>1</v>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>connector, battery control header family, plated-material engineering reference</t>
+        </is>
+      </c>
+      <c r="I1644" t="inlineStr">
+        <is>
+          <t>connector, battery control header family, plated-material engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1645">
+        <v>0.13581418990818575</v>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1645" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B1646">
+        <v>0.02272660887810803</v>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I1646" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>market for tin</t>
+        </is>
+      </c>
+      <c r="B1647">
+        <v>0.0039931558057929115</v>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="I1647" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>market for phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="B1648">
+        <v>0.00017282971995671607</v>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+      <c r="I1648" t="inlineStr">
+        <is>
+          <t>phosphorus, white, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>market for gold</t>
+        </is>
+      </c>
+      <c r="B1649">
+        <v>0.00025333548223235755</v>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="I1649" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B1650">
+        <v>0.0013906889757348967</v>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I1650" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>market for nylon 6</t>
+        </is>
+      </c>
+      <c r="B1651">
+        <v>0.6217965391241506</v>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+      <c r="I1651" t="inlineStr">
+        <is>
+          <t>nylon 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>market for glass fibre</t>
+        </is>
+      </c>
+      <c r="B1652">
+        <v>0.2664842310532074</v>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+      <c r="I1652" t="inlineStr">
+        <is>
+          <t>glass fibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1653">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1653" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1654">
+        <v>1</v>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1654" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -6035,7 +6035,7 @@
     <row r="299" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A299" t="inlineStr">
         <is>
-          <t>lithium foil rolling service, engineering reference</t>
+          <t xml:space="preserve">lithium foil rolling</t>
         </is>
       </c>
       <c r="B299" s="5">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>lithium foil rolling service, engineering reference</t>
+          <t xml:space="preserve">lithium foil rolling</t>
         </is>
       </c>
       <c r="H299" s="10" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,8 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery central controls and protection, engineering reference. Former reference product: battery central controls and protection, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
         </is>
@@ -15666,7 +15667,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B1088">
@@ -15689,14 +15690,14 @@
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery central control, mounted</t>
         </is>
       </c>
       <c r="B1089">
@@ -15719,7 +15720,7 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery central control, mounted</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15822,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>battery liquid cooling, 10 kg engineering reference</t>
+          <t xml:space="preserve">battery cooling system production, liquid cooling</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15856,7 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>battery liquid cooling, 10 kg engineering reference</t>
+          <t xml:space="preserve">battery cooling system, liquid cooling</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15892,8 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery liquid cooling, 10 kg engineering reference. Former reference product: battery liquid cooling, 10 kg engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15949,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>battery liquid cooling, 10 kg engineering reference</t>
+          <t xml:space="preserve">battery cooling system production, liquid cooling</t>
         </is>
       </c>
       <c r="B1104">
@@ -15970,7 +15972,7 @@
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>battery liquid cooling, 10 kg engineering reference</t>
+          <t xml:space="preserve">battery cooling system, liquid cooling</t>
         </is>
       </c>
     </row>
@@ -16312,7 +16314,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system production, 16 modules</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16348,7 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system, 16 modules</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16384,8 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery controls and cooling, 16-module engineering reference. Former reference product: battery controls and cooling, 16-module engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING CONTROL/THERMAL COVERAGE, item13, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 S26/S27; original Ellingsen2014 SI S39/S40, DOI10.1111/jiec.12072. Separate module monitoring from central protection: per16-module reference,1.1kg populated PCB monitors, central0.49kg populated PCB+2.8kg HV system+1.2kg LV system+.028kg fasteners=4.518kg. Use existing HV/LV/fastener process providers and generic populated through-hole PCB perkg; this is an explicit board-technology/material proxy rather than the source-specific board fabrication model. No whole BMS is added on top. Adopt one nominal10kg liquid-cooling assembly per reference: Al9.08, steel.23, PVC/rubber pipe.0096, thermal pad.2 (silicon.06, glass.02, ABS.12), ethylene glycol.48kg; source-rounded sum9.9996kg. Metal working/injection services are included; 100percent retention of listed finished materials is assumed. No stationary rack housing/container, common vehicle body or roadway is added. Monitoring/protection/cooling are added once as a unit-valued capacity input; kg module and matching waste remain separate, so density learning does not shrink fixed controls. Central and cooling hardware are conservatively co-replaced with each delivered pack; longer independent hardware life is not established. End-of-life uses the existing generic used Li-ion route for15.6176kg of auxiliary hardware per reference, without recovery credits; this is a treatment proxy for controls/cooling, not proof of chemistry-specific recovery. Source thermal duty, pump/radiator performance, protection ratings, inverter/pack interface, full outer pack enclosure and vehicle-specific module topology remain coverage/design gaps. The SIB cell-mass-equivalent module retains its existing18.768kg cell+6.203kg module hardware reference; it is not a demonstrated integer21700-cell topology. LiS uses the corrected19.306152kg cell+6.203kg module hardware. These are engineering references, not fleet-validated designs; use0.5-2x auxiliary-size and independent-replacement-life sensitivities.</t>
         </is>
@@ -16440,7 +16443,7 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system production, 16 modules</t>
         </is>
       </c>
       <c r="B1127">
@@ -16463,14 +16466,14 @@
       </c>
       <c r="G1127" t="inlineStr">
         <is>
-          <t>battery controls and cooling, 16-module engineering reference</t>
+          <t xml:space="preserve">battery control and cooling system, 16 modules</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B1128">
@@ -16493,14 +16496,14 @@
       </c>
       <c r="G1128" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B1129">
@@ -16523,14 +16526,14 @@
       </c>
       <c r="G1129" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>battery liquid cooling, 10 kg engineering reference</t>
+          <t xml:space="preserve">battery cooling system production, liquid cooling</t>
         </is>
       </c>
       <c r="B1130">
@@ -16553,7 +16556,7 @@
       </c>
       <c r="G1130" t="inlineStr">
         <is>
-          <t>battery liquid cooling, 10 kg engineering reference</t>
+          <t xml:space="preserve">battery cooling system, liquid cooling</t>
         </is>
       </c>
     </row>
@@ -16595,7 +16598,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>lithium foil rolling service, engineering reference</t>
+          <t xml:space="preserve">lithium foil rolling</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16632,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>lithium foil rolling service, engineering reference</t>
+          <t xml:space="preserve">lithium foil rolling</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16668,8 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>APPROVED LITHIUM-FOIL ROLLING ENGINEERING REFERENCE, item31, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 TableS17 requires lithium-adapted rolling; processing assumptions below are an engineering completion, not reported measurements. Replace the ordinary aluminium-specific rolling service at4.95kgprocessed/kgfinishedLi foil by a dedicated material-neutral mechanical rolling service. Assume0.5kWh electricity perkg rolling throughput, hence2.475kWh perkgfinishedfoil additionally to source2.1kWh generalprocess electricity,4.2MJ cooling and5MJheat retained once. This represents4.95kg cumulative rolling throughput, NOT4.95kg retained lithium or a measured pass count. Assume98percent final lithium retention:1/0.98=1.0204081632653061kg Li from source electrolysis perkgfoil;0.02040816326530612kg process loss. No aluminium feed or aluminium scrap is inherited; ordinary Al rolling elsewhere unchanged. Treat loss through existing hazardous-waste incineration as an explicit reactive-lithium fate proxy; real inert handling/passivation and associated emissions are not modeled. No lithium recovery/secondary-supply credit. Source/reference utilities are engineering proxies; atmosphere/inert gas, lubrication, facility and practical rolling yield/energy remain gaps. Sensitivities90-100percent yield and0.1-1kWh/kg throughput; energy does not scale with yield here because throughput is declared perkgfinishedfoil. No source-specific measured yield is claimed.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: lithium foil rolling service, engineering reference. Former reference product: lithium foil rolling service, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED LITHIUM-FOIL ROLLING ENGINEERING REFERENCE, item31, 2026-10-18. Wickerts corrected SI DOI10.1021/acssuschemeng.4c01782.s001 TableS17 requires lithium-adapted rolling; processing assumptions below are an engineering completion, not reported measurements. Replace the ordinary aluminium-specific rolling service at4.95kgprocessed/kgfinishedLi foil by a dedicated material-neutral mechanical rolling service. Assume0.5kWh electricity perkg rolling throughput, hence2.475kWh perkgfinishedfoil additionally to source2.1kWh generalprocess electricity,4.2MJ cooling and5MJheat retained once. This represents4.95kg cumulative rolling throughput, NOT4.95kg retained lithium or a measured pass count. Assume98percent final lithium retention:1/0.98=1.0204081632653061kg Li from source electrolysis perkgfoil;0.02040816326530612kg process loss. No aluminium feed or aluminium scrap is inherited; ordinary Al rolling elsewhere unchanged. Treat loss through existing hazardous-waste incineration as an explicit reactive-lithium fate proxy; real inert handling/passivation and associated emissions are not modeled. No lithium recovery/secondary-supply credit. Source/reference utilities are engineering proxies; atmosphere/inert gas, lubrication, facility and practical rolling yield/energy remain gaps. Sensitivities90-100percent yield and0.1-1kWh/kg throughput; energy does not scale with yield here because throughput is declared perkgfinishedfoil. No source-specific measured yield is claimed.</t>
         </is>
       </c>
     </row>
@@ -16721,7 +16725,7 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>lithium foil rolling service, engineering reference</t>
+          <t xml:space="preserve">lithium foil rolling</t>
         </is>
       </c>
       <c r="B1143">
@@ -16744,7 +16748,7 @@
       </c>
       <c r="G1143" t="inlineStr">
         <is>
-          <t>lithium foil rolling service, engineering reference</t>
+          <t xml:space="preserve">lithium foil rolling</t>
         </is>
       </c>
     </row>
@@ -16786,7 +16790,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit production, copper wire bonding</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16824,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit, copper wire bonding</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16860,8 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitor semiconductor, declared copper-wire package reference. Former reference product: battery monitor semiconductor, declared copper-wire package reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.</t>
         </is>
       </c>
     </row>
@@ -16912,7 +16917,7 @@
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit production, copper wire bonding</t>
         </is>
       </c>
       <c r="B1156">
@@ -16935,7 +16940,7 @@
       </c>
       <c r="G1156" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit, copper wire bonding</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17402,7 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery central control, mounted</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17436,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery central control, mounted</t>
         </is>
       </c>
     </row>
@@ -17467,7 +17472,8 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery central control board, engineering material reference. Former reference product: battery central control board, engineering material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17538,7 +17544,7 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery central control, mounted</t>
         </is>
       </c>
       <c r="B1183">
@@ -17561,12 +17567,12 @@
       </c>
       <c r="G1183" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery central control, mounted</t>
         </is>
       </c>
       <c r="I1183" t="inlineStr">
         <is>
-          <t>battery central control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery central control, mounted</t>
         </is>
       </c>
     </row>
@@ -17818,7 +17824,7 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector production, battery control board, plated contacts</t>
         </is>
       </c>
       <c r="B1191">
@@ -17841,19 +17847,19 @@
       </c>
       <c r="G1191" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
       <c r="I1191" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
       <c r="B1192">
@@ -17876,7 +17882,7 @@
       </c>
       <c r="G1192" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
       <c r="I1192" t="inlineStr">
@@ -17888,7 +17894,7 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0603</t>
         </is>
       </c>
       <c r="B1193">
@@ -17911,7 +17917,7 @@
       </c>
       <c r="G1193" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
       <c r="I1193" t="inlineStr">
@@ -17923,7 +17929,7 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor production</t>
         </is>
       </c>
       <c r="B1194">
@@ -17946,7 +17952,7 @@
       </c>
       <c r="G1194" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
       <c r="I1194" t="inlineStr">
@@ -17993,7 +17999,7 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1196">
@@ -18016,7 +18022,7 @@
       </c>
       <c r="G1196" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1196" t="inlineStr">
@@ -18068,7 +18074,7 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18108,7 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18144,8 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery module control board, engineering material reference. Former reference product: battery module control board, engineering material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18209,7 +18216,7 @@
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B1209">
@@ -18232,12 +18239,12 @@
       </c>
       <c r="G1209" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I1209" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18496,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit production, copper wire bonding</t>
         </is>
       </c>
       <c r="B1217">
@@ -18512,19 +18519,19 @@
       </c>
       <c r="G1217" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit, copper wire bonding</t>
         </is>
       </c>
       <c r="I1217" t="inlineStr">
         <is>
-          <t>battery monitor semiconductor, declared copper-wire package reference</t>
+          <t xml:space="preserve">battery monitoring integrated circuit, copper wire bonding</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector production, battery control board, plated contacts</t>
         </is>
       </c>
       <c r="B1218">
@@ -18547,19 +18554,19 @@
       </c>
       <c r="G1218" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
       <c r="I1218" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, TXU0204QPWRQ1</t>
         </is>
       </c>
       <c r="B1219">
@@ -18582,7 +18589,7 @@
       </c>
       <c r="G1219" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, TXU0204QPWRQ1</t>
         </is>
       </c>
       <c r="I1219" t="inlineStr">
@@ -18664,7 +18671,7 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, LM5168FQDDARQ1</t>
         </is>
       </c>
       <c r="B1222">
@@ -18687,7 +18694,7 @@
       </c>
       <c r="G1222" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, LM5168FQDDARQ1</t>
         </is>
       </c>
       <c r="I1222" t="inlineStr">
@@ -18699,7 +18706,7 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly production, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
       <c r="B1223">
@@ -18722,7 +18729,7 @@
       </c>
       <c r="G1223" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
       <c r="I1223" t="inlineStr">
@@ -18734,7 +18741,7 @@
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly production, battery monitoring board, 128 resistors</t>
         </is>
       </c>
       <c r="B1224">
@@ -18757,7 +18764,7 @@
       </c>
       <c r="G1224" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly, battery monitoring board, 128 resistors</t>
         </is>
       </c>
       <c r="I1224" t="inlineStr">
@@ -18804,7 +18811,7 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1226">
@@ -18827,7 +18834,7 @@
       </c>
       <c r="G1226" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1226" t="inlineStr">
@@ -18879,7 +18886,7 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18920,7 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -18949,7 +18956,8 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: barium titanate, capacitor ceramic engineering reference. Former reference product: barium titanate, capacitor ceramic engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -19010,7 +19018,7 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
       <c r="B1239">
@@ -19033,12 +19041,12 @@
       </c>
       <c r="G1239" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
       <c r="I1239" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19228,7 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate production, for capacitors</t>
         </is>
       </c>
     </row>
@@ -19254,7 +19262,7 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -19290,7 +19298,8 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: calcium zirconate, capacitor ceramic engineering reference. Former reference product: calcium zirconate, capacitor ceramic engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -19351,7 +19360,7 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate production, for capacitors</t>
         </is>
       </c>
       <c r="B1256">
@@ -19374,12 +19383,12 @@
       </c>
       <c r="G1256" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate, for capacitors</t>
         </is>
       </c>
       <c r="I1256" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19570,7 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0402</t>
         </is>
       </c>
     </row>
@@ -19595,7 +19604,7 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0402</t>
         </is>
       </c>
     </row>
@@ -19631,7 +19640,8 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor, Class2, 0402, declared material engineering reference. Former reference product: capacitor, Class2, 0402, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -19692,7 +19702,7 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0402</t>
         </is>
       </c>
       <c r="B1273">
@@ -19715,19 +19725,19 @@
       </c>
       <c r="G1273" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0402</t>
         </is>
       </c>
       <c r="I1273" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0402</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
       <c r="B1274">
@@ -19750,12 +19760,12 @@
       </c>
       <c r="G1274" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
       <c r="I1274" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -19977,7 +19987,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0603</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20021,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
     </row>
@@ -20047,7 +20057,8 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor, Class2, 0603, declared material engineering reference. Former reference product: capacitor, Class2, 0603, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20119,7 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0603</t>
         </is>
       </c>
       <c r="B1292">
@@ -20131,19 +20142,19 @@
       </c>
       <c r="G1292" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
       <c r="I1292" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
       <c r="B1293">
@@ -20166,12 +20177,12 @@
       </c>
       <c r="G1293" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
       <c r="I1293" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20404,7 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0805</t>
         </is>
       </c>
     </row>
@@ -20427,7 +20438,7 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0805</t>
         </is>
       </c>
     </row>
@@ -20463,7 +20474,8 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor, Class2, 0805, declared material engineering reference. Former reference product: capacitor, Class2, 0805, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -20524,7 +20536,7 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0805</t>
         </is>
       </c>
       <c r="B1311">
@@ -20547,19 +20559,19 @@
       </c>
       <c r="G1311" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0805</t>
         </is>
       </c>
       <c r="I1311" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0805</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
       <c r="B1312">
@@ -20582,12 +20594,12 @@
       </c>
       <c r="G1312" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
       <c r="I1312" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20821,7 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 1206</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20855,7 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 1206</t>
         </is>
       </c>
     </row>
@@ -20879,7 +20891,8 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor, Class2, 1206, declared material engineering reference. Former reference product: capacitor, Class2, 1206, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -20940,7 +20953,7 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 1206</t>
         </is>
       </c>
       <c r="B1330">
@@ -20963,19 +20976,19 @@
       </c>
       <c r="G1330" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 1206</t>
         </is>
       </c>
       <c r="I1330" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 1206</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
       <c r="B1331">
@@ -20998,12 +21011,12 @@
       </c>
       <c r="G1331" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
       <c r="I1331" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21238,7 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, flexible, class 2, 0805</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21272,7 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, flexible, class 2, 0805</t>
         </is>
       </c>
     </row>
@@ -21295,7 +21308,8 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor, flex Class2, 0805, declared material engineering reference. Former reference product: capacitor, flex Class2, 0805, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -21356,7 +21370,7 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, flexible, class 2, 0805</t>
         </is>
       </c>
       <c r="B1349">
@@ -21379,19 +21393,19 @@
       </c>
       <c r="G1349" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, flexible, class 2, 0805</t>
         </is>
       </c>
       <c r="I1349" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, flexible, class 2, 0805</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate production, for capacitors</t>
         </is>
       </c>
       <c r="B1350">
@@ -21414,12 +21428,12 @@
       </c>
       <c r="G1350" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
       <c r="I1350" t="inlineStr">
         <is>
-          <t>barium titanate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">barium titanate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21690,7 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, C0G, 0402</t>
         </is>
       </c>
     </row>
@@ -21710,7 +21724,7 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, C0G, 0402</t>
         </is>
       </c>
     </row>
@@ -21746,7 +21760,8 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor, C0G, 0402, declared material engineering reference. Former reference product: capacitor, C0G, 0402, declared material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -21807,7 +21822,7 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, C0G, 0402</t>
         </is>
       </c>
       <c r="B1369">
@@ -21830,19 +21845,19 @@
       </c>
       <c r="G1369" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, C0G, 0402</t>
         </is>
       </c>
       <c r="I1369" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, C0G, 0402</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate production, for capacitors</t>
         </is>
       </c>
       <c r="B1370">
@@ -21865,12 +21880,12 @@
       </c>
       <c r="G1370" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate, for capacitors</t>
         </is>
       </c>
       <c r="I1370" t="inlineStr">
         <is>
-          <t>calcium zirconate, capacitor ceramic engineering reference</t>
+          <t xml:space="preserve">calcium zirconate, for capacitors</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22107,7 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly production, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22141,7 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
     </row>
@@ -22162,7 +22177,8 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: capacitor set, 134 fitted battery monitor parts, engineering reference. Former reference product: capacitor set, 134 fitted battery monitor parts, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CERAMIC-CAPACITOR MATERIAL FAMILIES, issue55, 2026-10-18. YAGEO/KEMET June2026 MCD-Ceramic.pdf Annex1 Class2,Annex2 flex,Annex3 C0G https://yageogroup.com/content/Resource%20Library/Material%20Declaration/MCD-Ceramic.pdf ; TI TIDA020076 fitted BOM SLURB87; KEMET C0402C120J3GACAUTO datasheet1.06mg. Source-family material transfer is an engineering analogue for other manufacturers, not exactpart substitution. Separate BaTiO3 Class2, flexible Ag-epoxy termination and CaZrO3 C0G; do not model all ceramics as barite,allBaTiO3 or universalPd-bearing electrodes. Use declared percase Ni/Cu/Sn/Ag and ceramic masses. Keep miscellaneous composition explicitly unresolved: no inventedzeroPd proof or assignment of all dopants tooneoxide. ActualTi,Murata,TDK part-grade material/yields remain unmeasured; engineer source-family proxies preserving function/classes. Calcine BaCO3+TiO2-&gt;BaTiO3+CO2 and CaCO3+ZrO2-&gt;CaZrO3+CO2 at nominalpurestoichiometry,3MJ/kgheat+0.5kWh/kg milling assumptions. No orebarite substituted for refinedcarbonate. Componentmanufacture95%retention for knownmaterials with equalmixedsolidwaste,1kWh/kg+5MJ/kgprocessreference; actualpowderprocessing,cofiring/plating losses,water and emissions are gaps. Unknownretainedfraction and its manufacturingloss are not fabricated. Provideroutputs1kg finishedpart includingexplicitunknownmass; knownmaterialcoverage reported rather than normalizedto100%. TI70gmonitorboard has134fittedceramicparts:55Class2 0402,27Class2 0603,38Class2 0805,6Class2 1206,1flex0805,7C0G0402.2KEMETC0G parts use1.06mg each,other5use1.2mgfamilyreference. Not-fittedparts excluded. Preserveoriginalboardtotalmass by transferringcomponentmass difference to/from its explicitlyunresolvedresidualcomponentproxy; do not normalize allboardingredients. Centralboard2gcapacitor allowance becomesClass2 0603family analogue,stillunvalidated counts. Othergenericboard/passiveinputs remainuntiltheirscopedreferencesaredefined; native suppliers are untouched. Existingassemblysolder remainsseparate fromcomponentterminationSn. Existingcontrol/endoflife massbudgetsunchanged. Retain genuinelegacyPd recipes for otherconsumers and document unresolvedtrace dopants; no globalmetalCFedit or primary-secondaryclaim. Sensitivities90-100%retention,case-specificdesign,ceramicdopants andprecious-metal terminationchoices.</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22239,7 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly production, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
       <c r="B1388">
@@ -22246,19 +22262,19 @@
       </c>
       <c r="G1388" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
       <c r="I1388" t="inlineStr">
         <is>
-          <t>capacitor set, 134 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">capacitor assembly, battery monitoring board, 134 capacitors</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0402</t>
         </is>
       </c>
       <c r="B1389">
@@ -22281,19 +22297,19 @@
       </c>
       <c r="G1389" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0402</t>
         </is>
       </c>
       <c r="I1389" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0402</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0603</t>
         </is>
       </c>
       <c r="B1390">
@@ -22316,19 +22332,19 @@
       </c>
       <c r="G1390" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
       <c r="I1390" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0805</t>
         </is>
       </c>
       <c r="B1391">
@@ -22351,19 +22367,19 @@
       </c>
       <c r="G1391" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0805</t>
         </is>
       </c>
       <c r="I1391" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0805</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 1206</t>
         </is>
       </c>
       <c r="B1392">
@@ -22386,19 +22402,19 @@
       </c>
       <c r="G1392" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 1206</t>
         </is>
       </c>
       <c r="I1392" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 1206, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 1206</t>
         </is>
       </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, flexible, class 2, 0805</t>
         </is>
       </c>
       <c r="B1393">
@@ -22421,19 +22437,19 @@
       </c>
       <c r="G1393" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, flexible, class 2, 0805</t>
         </is>
       </c>
       <c r="I1393" t="inlineStr">
         <is>
-          <t>capacitor, flex Class2, 0805, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, flexible, class 2, 0805</t>
         </is>
       </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, C0G, 0402</t>
         </is>
       </c>
       <c r="B1394">
@@ -22456,12 +22472,12 @@
       </c>
       <c r="G1394" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, C0G, 0402</t>
         </is>
       </c>
       <c r="I1394" t="inlineStr">
         <is>
-          <t>capacitor, C0G, 0402, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, C0G, 0402</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22489,7 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide production, for resistor films</t>
         </is>
       </c>
     </row>
@@ -22507,7 +22523,7 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide, for resistor films</t>
         </is>
       </c>
     </row>
@@ -22543,7 +22559,8 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: ruthenium dioxide, resistor film engineering reference. Former reference product: ruthenium dioxide, resistor film engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
         </is>
       </c>
     </row>
@@ -22604,7 +22621,7 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide production, for resistor films</t>
         </is>
       </c>
       <c r="B1406">
@@ -22627,12 +22644,12 @@
       </c>
       <c r="G1406" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide, for resistor films</t>
         </is>
       </c>
       <c r="I1406" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide, for resistor films</t>
         </is>
       </c>
     </row>
@@ -22784,7 +22801,7 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide production, for resistor glass</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22835,7 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide, for resistor glass</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22871,8 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps. PbO made from Pb and oxygen at stoichiometry; heat proxy, not measured lead-glass processing.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: lead oxide, resistor glass engineering reference. Former reference product: lead oxide, resistor glass engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps. PbO made from Pb and oxygen at stoichiometry; heat proxy, not measured lead-glass processing.</t>
         </is>
       </c>
     </row>
@@ -22915,7 +22933,7 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide production, for resistor glass</t>
         </is>
       </c>
       <c r="B1422">
@@ -22938,12 +22956,12 @@
       </c>
       <c r="G1422" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide, for resistor glass</t>
         </is>
       </c>
       <c r="I1422" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide, for resistor glass</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23078,7 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor production</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23112,7 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23148,8 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: thick-film resistor, declared-material engineering reference. Former reference product: thick-film resistor, declared-material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23210,7 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor production</t>
         </is>
       </c>
       <c r="B1437">
@@ -23214,12 +23233,12 @@
       </c>
       <c r="G1437" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
       <c r="I1437" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
     </row>
@@ -23506,7 +23525,7 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide production, for resistor glass</t>
         </is>
       </c>
       <c r="B1446">
@@ -23529,19 +23548,19 @@
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide, for resistor glass</t>
         </is>
       </c>
       <c r="I1446" t="inlineStr">
         <is>
-          <t>lead oxide, resistor glass engineering reference</t>
+          <t xml:space="preserve">lead oxide, for resistor glass</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide production, for resistor films</t>
         </is>
       </c>
       <c r="B1447">
@@ -23564,12 +23583,12 @@
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide, for resistor films</t>
         </is>
       </c>
       <c r="I1447" t="inlineStr">
         <is>
-          <t>ruthenium dioxide, resistor film engineering reference</t>
+          <t xml:space="preserve">ruthenium dioxide, for resistor films</t>
         </is>
       </c>
     </row>
@@ -23721,7 +23740,7 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper production</t>
         </is>
       </c>
     </row>
@@ -23755,7 +23774,7 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper</t>
         </is>
       </c>
     </row>
@@ -23791,7 +23810,8 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: zero-ohm jumper, declared-material engineering reference. Former reference product: zero-ohm jumper, declared-material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
         </is>
       </c>
     </row>
@@ -23852,7 +23872,7 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper production</t>
         </is>
       </c>
       <c r="B1463">
@@ -23875,12 +23895,12 @@
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper</t>
         </is>
       </c>
       <c r="I1463" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper</t>
         </is>
       </c>
     </row>
@@ -24277,7 +24297,7 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly production, battery monitoring board, 128 resistors</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24331,7 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly, battery monitoring board, 128 resistors</t>
         </is>
       </c>
     </row>
@@ -24347,7 +24367,8 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: resistor set, 128 fitted battery monitor parts, engineering reference. Former reference product: resistor set, 128 fitted battery monitor parts, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED RESISTOR FUNCTION/MATERIAL REFERENCE, issue56, 2026-10-18. Bourns CR0603 Material Declaration,2022-08-01, https://www.bourns.com/docs/product-mds/cr0603_mds.pdf?sfvrsn=d79410bf_3 (manufacturer indexed declaration; direct download currently errors). Vishay CRCW...C doc28773 https://www.vishay.com/docs/28773/crcwce3.pdf package masses; TI TIDA020076 SLURB87 fitted BOM. Use declared CR0603 1.9339mg classic thick-film composition as a scoped engineering analogue, not a claim of exact Vishay/Yageo paste chemistry. Ceramic1.6618mg=96%alumina/4%silica; conductor0.0447mg=95%Ag/5%glass; film0.0255mg=25%RuO2,40%Ag,15%Pd,20%lead-containingglass; epoxy0.0335mg; NiCr0.0025mg=80%Ni20%Cr; Ni0.0878mg; Sn0.0781mg. Lead-containingglass uses explicit30wt%PbO/70%silica assumption (test0-60%), never alllead. Ordinary conductor glass is flat-glass proxy. 17zero-ohm jumpers use same body/termination but film replaced byAg, a function-based engineering assumption; test alternative pastes rather than claiming analyticallyzeroPd. Retain legitimatePd/Ag/Ru in111nonzero resistors. Ru supplied by existing ZA ruthenium coproduct inventory, not silently substituted byPd; its historical PGM allocation remains unvalidated. RuO2 uses stoichiometric Ru+oxygen and3MJ/kgheat+0.5kWh/kgprocess proxies. 95%known-material retention with matched mixed manufacturing waste,1kWh/kg+5MJ/kg; supplier/plating/printing losses uncertain. Fittedcounts63x0402,21x0603,4x0805,38x1206,2x2010; zero counts1,12,4,0,0. Manufacturer family masses0.65,2,5.5,10mg for firstfour;2010=25.5mg explicit legacy-family engineering mass reference. No unmounted parts. Component mass difference goes to unresolved residual board proxy, preserving70g complete monitorboard; central3g allowance keeps its mass and uses nonzero-family analogue. TerminationSn and assembly solder remain separate. No native/global supplier edits, new EOL or precious-metal credit. Source specific paste variants, resistance dependence, actual Vishay grades, jumper film and2010 mass are coverage/sensitivity gaps.</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24429,7 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly production, battery monitoring board, 128 resistors</t>
         </is>
       </c>
       <c r="B1486">
@@ -24431,19 +24452,19 @@
       </c>
       <c r="G1486" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly, battery monitoring board, 128 resistors</t>
         </is>
       </c>
       <c r="I1486" t="inlineStr">
         <is>
-          <t>resistor set, 128 fitted battery monitor parts, engineering reference</t>
+          <t xml:space="preserve">resistor assembly, battery monitoring board, 128 resistors</t>
         </is>
       </c>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor production</t>
         </is>
       </c>
       <c r="B1487">
@@ -24466,19 +24487,19 @@
       </c>
       <c r="G1487" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
       <c r="I1487" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper production</t>
         </is>
       </c>
       <c r="B1488">
@@ -24501,12 +24522,12 @@
       </c>
       <c r="G1488" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper</t>
         </is>
       </c>
       <c r="I1488" t="inlineStr">
         <is>
-          <t>zero-ohm jumper, declared-material engineering reference</t>
+          <t xml:space="preserve">zero-ohm jumper</t>
         </is>
       </c>
     </row>
@@ -24518,7 +24539,7 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24573,7 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24609,8 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: semiconductor package, CC2662R1FTWRGZRQ1, declared material reference. Former reference product: semiconductor package, CC2662R1FTWRGZRQ1, declared material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24671,7 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
       <c r="B1500">
@@ -24672,12 +24694,12 @@
       </c>
       <c r="G1500" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
       <c r="I1500" t="inlineStr">
         <is>
-          <t>semiconductor package, CC2662R1FTWRGZRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, CC2662R1FTWRGZRQ1</t>
         </is>
       </c>
     </row>
@@ -25179,7 +25201,7 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, LM5168FQDDARQ1</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25235,7 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, LM5168FQDDARQ1</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25271,8 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: semiconductor package, LM5168FQDDARQ1, declared material reference. Former reference product: semiconductor package, LM5168FQDDARQ1, declared material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25333,7 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, LM5168FQDDARQ1</t>
         </is>
       </c>
       <c r="B1526">
@@ -25333,12 +25356,12 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, LM5168FQDDARQ1</t>
         </is>
       </c>
       <c r="I1526" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, LM5168FQDDARQ1</t>
         </is>
       </c>
     </row>
@@ -25875,7 +25898,7 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, TXU0204QPWRQ1</t>
         </is>
       </c>
     </row>
@@ -25909,7 +25932,7 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, TXU0204QPWRQ1</t>
         </is>
       </c>
     </row>
@@ -25945,7 +25968,8 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: semiconductor package, TXU0204QPWRQ1, declared material reference. Former reference product: semiconductor package, TXU0204QPWRQ1, declared material reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PACKAGE-SPECIFIC CONTROL SEMICONDUCTORS, issue57, 2026-10-18. TI manufacturer material-content reports https://www.ti.com/quality-reliability-packaging-download/de-de/report?opn=LM5168FQDDARQ1 ; ?opn=TXU0204QPWRQ1 ; ?opn=CC2662R1FTWRGZRQ1 , accessed2026-10-18; TI TIDA020076 fitted BOM and CC2662 WBMS controller guide. Use one explicitly selected first returned material declaration per part, never sum alternative assembly-site tables. LM5168 FlyBuck regulator,TXU0204 logic translator andCC2662 WBMS MCU have distinct die,frame,bonds,mold and plating. Sum constituent rows excluding subtotals to recover declared package mass. Retain actual Zn alloying,Ag attach and Au/Pd plating; no arbitraryZn-for-Sb conversion or global antimony deletion. Sb is not listed in these selected declarations, which is not proof of analyticalzeroSb in all electronics. Purchase fabricated die wafer area from declared Si mass at explicit300micrometrethickness,2330kg/m3; no second rawSi charge. Silica-sand supply is an explicit fused-silica proxy with missing fusion/purity energy. Fe uses lowalloy steel proxy, resin uses epoxy/phenolic analogues, elementalP/chlorine feeds are nominal material proxies. Proprietary composition remains unresolved. Package assembly1kWh/kg and100%final retention are engineering assumptions,not suppliermeasured yield or complete semiconductor packaging LCI. Module priorlogic allowances1.5g and0.4g are replaced by oneTXU and oneLM5168 package,consistent with fitted reference parts; released mass remains explicitly unresolved board components. Other actualMCU/isolation packages are still coveragegaps,not proven identical. Central5gMCU allowance becomes oneCC2662 (firstselectedsite) and residual mass,not dozens of fictitious MCU packages. BQ79616 monitor package unchanged. Fixed70g/490g board budgets and their downstream endoflife retained. No motherboard/chassis electronics added. Process service, film,purity,actualsite and unknown-component sensitivity remain necessary; no certifiedexactvehicleBOM claim.</t>
         </is>
       </c>
     </row>
@@ -26006,7 +26030,7 @@
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, TXU0204QPWRQ1</t>
         </is>
       </c>
       <c r="B1553">
@@ -26029,12 +26053,12 @@
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, TXU0204QPWRQ1</t>
         </is>
       </c>
       <c r="I1553" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, TXU0204QPWRQ1</t>
         </is>
       </c>
     </row>
@@ -26501,7 +26525,7 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
     </row>
@@ -26535,7 +26559,7 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -26571,7 +26595,8 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery auxiliary interface and power conditioning, engineering reference. Former reference product: battery auxiliary interface and power conditioning, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26657,7 @@
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1578">
@@ -26655,12 +26680,12 @@
       </c>
       <c r="G1578" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1578" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -26912,7 +26937,7 @@
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor production, class 2, 0603</t>
         </is>
       </c>
       <c r="B1586">
@@ -26935,19 +26960,19 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
       <c r="I1586" t="inlineStr">
         <is>
-          <t>capacitor, Class2, 0603, declared material engineering reference</t>
+          <t xml:space="preserve">capacitor, class 2, 0603</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor production</t>
         </is>
       </c>
       <c r="B1587">
@@ -26970,19 +26995,19 @@
       </c>
       <c r="G1587" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
       <c r="I1587" t="inlineStr">
         <is>
-          <t>thick-film resistor, declared-material engineering reference</t>
+          <t xml:space="preserve">thick-film resistor</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, TXU0204QPWRQ1</t>
         </is>
       </c>
       <c r="B1588">
@@ -27005,19 +27030,19 @@
       </c>
       <c r="G1588" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, TXU0204QPWRQ1</t>
         </is>
       </c>
       <c r="I1588" t="inlineStr">
         <is>
-          <t>semiconductor package, TXU0204QPWRQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, TXU0204QPWRQ1</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package production, LM5168FQDDARQ1</t>
         </is>
       </c>
       <c r="B1589">
@@ -27040,12 +27065,12 @@
       </c>
       <c r="G1589" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, LM5168FQDDARQ1</t>
         </is>
       </c>
       <c r="I1589" t="inlineStr">
         <is>
-          <t>semiconductor package, LM5168FQDDARQ1, declared material reference</t>
+          <t xml:space="preserve">semiconductor package, LM5168FQDDARQ1</t>
         </is>
       </c>
     </row>
@@ -27092,7 +27117,7 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -27126,7 +27151,7 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -27162,7 +27187,8 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-sulfur, Li-S, density-scaled reference. Former reference product: market for battery cells, Li-sulfur, Li-S, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27249,7 @@
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1602">
@@ -27246,12 +27272,12 @@
       </c>
       <c r="G1602" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1602" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-sulfur, Li-S, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-sulfur, Li-S, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -27473,7 +27499,7 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27507,7 +27533,7 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27543,7 +27569,9 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -27604,7 +27632,7 @@
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
       <c r="B1620">
@@ -27627,12 +27655,12 @@
       </c>
       <c r="G1620" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
       <c r="I1620" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -28064,7 +28092,7 @@
       </c>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector production, battery control board, plated contacts</t>
         </is>
       </c>
     </row>
@@ -28098,7 +28126,7 @@
       </c>
       <c r="B1638" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28162,8 @@
       </c>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: connector, battery control header family, plated-material engineering reference. Former reference product: connector, battery control header family, plated-material engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED BATTERY CONNECTOR MATERIAL/PLATING REFERENCE, issue68,2026-10-18. TI TIDA020076 SLURB87 fittedBOM:sixheaders,46pins. Molex manufacturer705510038(4pin,1.023g),705550045(11pin,2.564g),705550040(6pin,1.420g),https://www.molex.com/en-us/products/part-detail/705550045 ; matingAu0.381um,tailSn1.905um,brass/phosphorbronze,highTthermoplastic. SamtecFTSH-105-01-F-DV-K,10pin,LCP/phosphorbronze,3microinch=0.0762umselectiveAu,matteSn: https://suddendocs.samtec.com/prints/ftsh-1xx-xx-xxx-dv-xxx-xxx-mkt.pdf . Replace computerperipheralbusconnectors only in theexisting module/centralcontrolboards by a scopedcount-weightedheaderfamily. Actualfittedcohort=2x4pinMolex+2x11pinMolex+1x6pinMolex+1x10pinSamtec,not not-fittedconnectors. This defines referencecomposition; preserve20g/moduleboard and100g/centralboardconnector allowances because board-specific completeharness/matingconnectorcounts are unverified. These doses implyfractionalcohort equivalents,NOT a claimof sixheaders totalling20g or that thecentralboard has theTI layout. Thus materialproxy is improved while exactfullconnectorquantity remains a sourcegap. ForMolex36contacts use0.64mmsquaresection*10mmdevelopedlength,3mmmatingzone and3.30mmtail as explicitgeometryassumptions,not dimensionallycompleteCAD. Finishedmassusesmanufacturerweights; subtractAu/Ni/Snplate fromgeometricbulkmetal beforealloysplit,remainingmasshousing. Metalbaseengineering50/50brassCu70Zn30 andphosphorbronzeCu95.8Sn4P0.2; actualtwoallowedalloys proportions unknown. Samtecgeometry10x0.4mmsquare*(3.05+2.24+1)mmcontacts,6.2x3.43x2.24mmhousingminuspinholes;terminaldensity8800kg/m3,housing1400kg/m3 assumptions. Samtecactualnetmass unavailable; include calculatedhousing/contact/platingmass,not distributorpackagingweight. Nickelunderplate1.27um is a declaredengineeringassumption forbothfamilies,test0.5-2.5um; SamtectailSn1.905um borrowedMolexreference. Preserve trueAu,Ni,Sn,Cu,Zn,P; no zeroAu orallbulkmetal-as-gold. PA6/glassfiber70/30 is an explicitheat-resistantthermoplastic supplyproxy forMolex andLCP housing,not actualresinchemistry; resinflame-retardants andtraceadditives unresolved. Knownmaterialmanufacture95%retention withmatchedmixedwaste,1kWh/kgassemblyreference. Sensitivitycontactlength6-14mm,platedlength1-4mm,sourcegradevariantAu0.0762-0.762um,connectorallowance0.5-2x. No additionalboardarea,wholeelectronics orharness inventorydoublecount. Fixedboard/controlmass andexistingcompletecontrolEOL unchanged. These are actual referenceboardparts withunverifiedvehiclequalification,not certifiedautomotiveBOM.</t>
         </is>
       </c>
     </row>
@@ -28195,7 +28224,7 @@
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector production, battery control board, plated contacts</t>
         </is>
       </c>
       <c r="B1644">
@@ -28218,12 +28247,12 @@
       </c>
       <c r="G1644" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
       <c r="I1644" t="inlineStr">
         <is>
-          <t>connector, battery control header family, plated-material engineering reference</t>
+          <t xml:space="preserve">connector, battery control board, plated contacts</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -27533,7 +27533,7 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -27569,7 +27569,8 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-sulfur, Li-S, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -27645,7 +27646,7 @@
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1620" t="inlineStr">
@@ -27655,12 +27656,12 @@
       </c>
       <c r="G1620" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
       <c r="I1620" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-sulfur, Li-S, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-sulfur, Li-S, without cells and controls</t>
         </is>
       </c>
     </row>
